--- a/Planning-Template.xlsx
+++ b/Planning-Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franr\OneDrive\Escritorio\informatica_us\asignaturas\DP2\ent\Workspace-26\Projects\Acme-Starters-C\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E258BD7-A18C-4E3F-99CF-DB18BA672F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED9D66B-D0DD-421B-9137-D405D31496CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="2" xr2:uid="{683E09B8-1D94-4905-B116-9D998A46AAA3}"/>
   </bookViews>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="95">
   <si>
     <t xml:space="preserve">  Enter configuration data in these cells</t>
   </si>
@@ -338,6 +338,12 @@
   </si>
   <si>
     <t>T0002/D</t>
+  </si>
+  <si>
+    <t>Completed</t>
+  </si>
+  <si>
+    <t>T0004/D</t>
   </si>
 </sst>
 </file>
@@ -711,6 +717,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="22" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -728,9 +737,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1370,118 +1376,118 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="55" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
+      <c r="D5" s="54"/>
+      <c r="E5" s="54"/>
+      <c r="F5" s="54"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="54"/>
+      <c r="I5" s="54"/>
+      <c r="J5" s="54"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
+      <c r="B6" s="54"/>
+      <c r="C6" s="54"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="54"/>
+      <c r="F6" s="54"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="54"/>
+      <c r="I6" s="54"/>
+      <c r="J6" s="54"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="54"/>
+      <c r="D7" s="54"/>
+      <c r="E7" s="54"/>
+      <c r="F7" s="54"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="54"/>
+      <c r="J7" s="54"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="53"/>
+      <c r="B8" s="54"/>
+      <c r="C8" s="54"/>
+      <c r="D8" s="54"/>
+      <c r="E8" s="54"/>
+      <c r="F8" s="54"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="54"/>
+      <c r="I8" s="54"/>
+      <c r="J8" s="54"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="53"/>
+      <c r="B9" s="54"/>
+      <c r="C9" s="54"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="54"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="54"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
+      <c r="B10" s="54"/>
+      <c r="C10" s="54"/>
+      <c r="D10" s="54"/>
+      <c r="E10" s="54"/>
+      <c r="F10" s="54"/>
+      <c r="G10" s="54"/>
+      <c r="H10" s="54"/>
+      <c r="I10" s="54"/>
+      <c r="J10" s="54"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B11" s="53"/>
-      <c r="C11" s="53"/>
-      <c r="D11" s="53"/>
-      <c r="E11" s="53"/>
-      <c r="F11" s="53"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="53"/>
+      <c r="B11" s="54"/>
+      <c r="C11" s="54"/>
+      <c r="D11" s="54"/>
+      <c r="E11" s="54"/>
+      <c r="F11" s="54"/>
+      <c r="G11" s="54"/>
+      <c r="H11" s="54"/>
+      <c r="I11" s="54"/>
+      <c r="J11" s="54"/>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B12" s="53"/>
-      <c r="C12" s="53"/>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="53"/>
-      <c r="J12" s="53"/>
+      <c r="B12" s="54"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="54"/>
+      <c r="I12" s="54"/>
+      <c r="J12" s="54"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1499,17 +1505,17 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B3" s="2"/>
@@ -1523,39 +1529,39 @@
       <c r="J3" s="1"/>
     </row>
     <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7" s="1"/>
@@ -1583,29 +1589,29 @@
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9" s="4"/>
-      <c r="C9" s="55" t="s">
+      <c r="C9" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="D9" s="55"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="55"/>
-      <c r="J9" s="55"/>
+      <c r="D9" s="56"/>
+      <c r="E9" s="56"/>
+      <c r="F9" s="56"/>
+      <c r="G9" s="56"/>
+      <c r="H9" s="56"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="56"/>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B10" s="48"/>
-      <c r="C10" s="55" t="s">
+      <c r="C10" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
-      <c r="F10" s="55"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="55"/>
-      <c r="J10" s="55"/>
+      <c r="D10" s="56"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="56"/>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11" s="49"/>
@@ -1622,16 +1628,16 @@
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B12" s="3"/>
-      <c r="C12" s="55" t="s">
+      <c r="C12" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="55"/>
+      <c r="D12" s="56"/>
+      <c r="E12" s="56"/>
+      <c r="F12" s="56"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="56"/>
+      <c r="I12" s="56"/>
+      <c r="J12" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1655,40 +1661,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="C2" s="54" t="s">
+      <c r="C2" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="54"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C4" s="52" t="s">
+      <c r="C4" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
-      <c r="P4" s="52"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="53"/>
+      <c r="P4" s="53"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C5" s="5"/>
@@ -1707,7 +1713,7 @@
       <c r="P5" s="5"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="57" t="s">
         <v>67</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -1730,7 +1736,7 @@
       <c r="P6" s="5"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="C7" s="56"/>
+      <c r="C7" s="57"/>
       <c r="D7" s="11" t="s">
         <v>69</v>
       </c>
@@ -1748,19 +1754,19 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="57" t="s">
+      <c r="I9" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="J9" s="57"/>
+      <c r="J9" s="58"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="57" t="s">
+      <c r="L9" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="M9" s="57"/>
-      <c r="N9" s="57" t="s">
+      <c r="M9" s="58"/>
+      <c r="N9" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="O9" s="57"/>
+      <c r="O9" s="58"/>
       <c r="P9" s="7"/>
     </row>
     <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -1822,7 +1828,7 @@
         <v>63</v>
       </c>
       <c r="E11" s="42" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F11" s="42" t="s">
         <v>27</v>
@@ -1910,7 +1916,7 @@
         <v>61</v>
       </c>
       <c r="E13" s="42" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F13" s="42" t="s">
         <v>25</v>
@@ -1929,7 +1935,7 @@
       </c>
       <c r="K13" s="44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>Ongoing</v>
+        <v>Completed</v>
       </c>
       <c r="L13" s="46"/>
       <c r="M13" s="46"/>
@@ -1949,18 +1955,27 @@
       </c>
       <c r="C14" s="41" t="str">
         <f>IF(ISBLANK(D14), "", _xlfn.CONCAT("T", TEXT(B14, "0000"), "/", VLOOKUP(D14, Internal!$B$35:C$39, 2, FALSE), IF(OR(D14="QA", D14="Revision"), _xlfn.CONCAT("/", H14), "")))</f>
-        <v/>
-      </c>
-      <c r="D14" s="43"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="42"/>
+        <v>T0004/D</v>
+      </c>
+      <c r="D14" s="43" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" s="42" t="s">
+        <v>25</v>
+      </c>
+      <c r="G14" s="43" t="s">
+        <v>41</v>
+      </c>
+      <c r="H14" s="42" t="s">
+        <v>92</v>
+      </c>
       <c r="I14" s="45"/>
       <c r="J14" s="45"/>
-      <c r="K14" s="44" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
+      <c r="K14" s="44" t="s">
+        <v>93</v>
       </c>
       <c r="L14" s="46"/>
       <c r="M14" s="46"/>
@@ -1980,18 +1995,30 @@
       </c>
       <c r="C15" s="41" t="str">
         <f>IF(ISBLANK(D15), "", _xlfn.CONCAT("T", TEXT(B15, "0000"), "/", VLOOKUP(D15, Internal!$B$35:C$39, 2, FALSE), IF(OR(D15="QA", D15="Revision"), _xlfn.CONCAT("/", H15), "")))</f>
-        <v/>
-      </c>
-      <c r="D15" s="43"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="43"/>
+        <v>T0005/M</v>
+      </c>
+      <c r="D15" s="43" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="F15" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" s="43" t="s">
+        <v>36</v>
+      </c>
       <c r="H15" s="42"/>
-      <c r="I15" s="45"/>
-      <c r="J15" s="45"/>
+      <c r="I15" s="45">
+        <v>46063.479166666664</v>
+      </c>
+      <c r="J15" s="45">
+        <v>46063.5625</v>
+      </c>
       <c r="K15" s="44" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
+        <v>Completed</v>
       </c>
       <c r="L15" s="46"/>
       <c r="M15" s="46"/>
@@ -2011,13 +2038,23 @@
       </c>
       <c r="C16" s="41" t="str">
         <f>IF(ISBLANK(D16), "", _xlfn.CONCAT("T", TEXT(B16, "0000"), "/", VLOOKUP(D16, Internal!$B$35:C$39, 2, FALSE), IF(OR(D16="QA", D16="Revision"), _xlfn.CONCAT("/", H16), "")))</f>
-        <v/>
-      </c>
-      <c r="D16" s="43"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="42"/>
+        <v>T0006/M</v>
+      </c>
+      <c r="D16" s="43" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="43" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="42" t="s">
+        <v>94</v>
+      </c>
       <c r="I16" s="45"/>
       <c r="J16" s="45"/>
       <c r="K16" s="44" t="str">
@@ -5045,40 +5082,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="C2" s="54" t="s">
+      <c r="C2" s="55" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="54"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C4" s="52" t="s">
+      <c r="C4" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
-      <c r="P4" s="52"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="53"/>
+      <c r="P4" s="53"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C5" s="5"/>
@@ -5097,7 +5134,7 @@
       <c r="P5" s="5"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="57" t="s">
         <v>67</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -5120,7 +5157,7 @@
       <c r="P6" s="5"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="C7" s="56"/>
+      <c r="C7" s="57"/>
       <c r="D7" s="11" t="s">
         <v>69</v>
       </c>
@@ -5138,19 +5175,19 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="57" t="s">
+      <c r="I9" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="J9" s="57"/>
+      <c r="J9" s="58"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="57" t="s">
+      <c r="L9" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="M9" s="57"/>
-      <c r="N9" s="57" t="s">
+      <c r="M9" s="58"/>
+      <c r="N9" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="O9" s="57"/>
+      <c r="O9" s="58"/>
       <c r="P9" s="7"/>
     </row>
     <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -8394,40 +8431,40 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="C2" s="54" t="s">
+      <c r="C2" s="55" t="s">
         <v>85</v>
       </c>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="54"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
     </row>
     <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="C4" s="52" t="s">
+      <c r="C4" s="53" t="s">
         <v>74</v>
       </c>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
-      <c r="P4" s="52"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
+      <c r="K4" s="53"/>
+      <c r="L4" s="53"/>
+      <c r="M4" s="53"/>
+      <c r="N4" s="53"/>
+      <c r="O4" s="53"/>
+      <c r="P4" s="53"/>
     </row>
     <row r="5" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C5" s="5"/>
@@ -8446,7 +8483,7 @@
       <c r="P5" s="5"/>
     </row>
     <row r="6" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="57" t="s">
         <v>67</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -8469,7 +8506,7 @@
       <c r="P6" s="5"/>
     </row>
     <row r="7" spans="2:16" x14ac:dyDescent="0.35">
-      <c r="C7" s="56"/>
+      <c r="C7" s="57"/>
       <c r="D7" s="11" t="s">
         <v>69</v>
       </c>
@@ -8487,19 +8524,19 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="57" t="s">
+      <c r="I9" s="58" t="s">
         <v>51</v>
       </c>
-      <c r="J9" s="57"/>
+      <c r="J9" s="58"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="57" t="s">
+      <c r="L9" s="58" t="s">
         <v>7</v>
       </c>
-      <c r="M9" s="57"/>
-      <c r="N9" s="57" t="s">
+      <c r="M9" s="58"/>
+      <c r="N9" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="O9" s="57"/>
+      <c r="O9" s="58"/>
       <c r="P9" s="7"/>
     </row>
     <row r="10" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -11742,52 +11779,52 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B4" s="52" t="s">
+      <c r="B4" s="53" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
+      <c r="C4" s="53"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="53"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="53"/>
+      <c r="H4" s="53"/>
+      <c r="I4" s="53"/>
+      <c r="J4" s="53"/>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="53"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="52"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="53"/>
+      <c r="H6" s="53"/>
+      <c r="I6" s="53"/>
+      <c r="J6" s="53"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7" s="5"/>
@@ -11992,7 +12029,7 @@
       <c r="J22" s="12"/>
     </row>
     <row r="23" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B23" s="58">
+      <c r="B23" s="52">
         <v>46062.354166666664</v>
       </c>
       <c r="C23" s="12"/>

--- a/Planning-Template.xlsx
+++ b/Planning-Template.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\FrankitoJR\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alvar\Desktop\DP2-2526\Workspace-26\Projects\Acme-Starters\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A9C75F-8E27-43A7-BA1E-8C4685D37663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CC2C1CD-94BA-4120-82C1-850708545C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-5340" yWindow="-16320" windowWidth="38640" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Copyright" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="161">
   <si>
     <t>Copyright</t>
   </si>
@@ -500,6 +500,42 @@
   </si>
   <si>
     <t>Crear Entidad Donación y método de pago</t>
+  </si>
+  <si>
+    <t>Implementar Become Sponsor</t>
+  </si>
+  <si>
+    <t>Crear Entidad Sponsorship, Donation y Sponsor</t>
+  </si>
+  <si>
+    <t>T0034/D</t>
+  </si>
+  <si>
+    <t>T0035/M</t>
+  </si>
+  <si>
+    <t>T0036/D</t>
+  </si>
+  <si>
+    <t>T0037/D</t>
+  </si>
+  <si>
+    <t>T0038/QA</t>
+  </si>
+  <si>
+    <t>T0039/D</t>
+  </si>
+  <si>
+    <t>T0040/QA</t>
+  </si>
+  <si>
+    <t>T0041/QA</t>
+  </si>
+  <si>
+    <t>Test Legal y Hacking de todo lo relacionado con el nivel B</t>
+  </si>
+  <si>
+    <t>Redactar documento de Testing Report</t>
   </si>
 </sst>
 </file>
@@ -511,7 +547,7 @@
     <numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm"/>
     <numFmt numFmtId="166" formatCode="dd/mm/yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -560,6 +596,12 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
@@ -905,6 +947,21 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="6" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -920,26 +977,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="8">
+  <dxfs count="7">
     <dxf>
       <font>
         <sz val="11"/>
@@ -1004,6 +1046,7 @@
         <color rgb="FFFFFF00"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
+        <charset val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1017,20 +1060,6 @@
         <color rgb="FFFFFF00"/>
         <name val="Aptos Narrow"/>
         <family val="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="11"/>
-        <color rgb="FFFFFF00"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <charset val="1"/>
       </font>
       <fill>
         <patternFill>
@@ -1703,124 +1732,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:AMJ12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1024" width="9.140625" style="2"/>
+    <col min="1" max="1024" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="54" t="s">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-    </row>
-    <row r="4" spans="2:10" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="55" t="s">
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+    </row>
+    <row r="4" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
-      <c r="F6" s="55"/>
-      <c r="G6" s="55"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="55"/>
-      <c r="J6" s="55"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="55"/>
-      <c r="E7" s="55"/>
-      <c r="F7" s="55"/>
-      <c r="G7" s="55"/>
-      <c r="H7" s="55"/>
-      <c r="I7" s="55"/>
-      <c r="J7" s="55"/>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
-      <c r="D8" s="55"/>
-      <c r="E8" s="55"/>
-      <c r="F8" s="55"/>
-      <c r="G8" s="55"/>
-      <c r="H8" s="55"/>
-      <c r="I8" s="55"/>
-      <c r="J8" s="55"/>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B9" s="55"/>
-      <c r="C9" s="55"/>
-      <c r="D9" s="55"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="55"/>
-      <c r="J9" s="55"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
-      <c r="D10" s="55"/>
-      <c r="E10" s="55"/>
-      <c r="F10" s="55"/>
-      <c r="G10" s="55"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="55"/>
-      <c r="J10" s="55"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B11" s="55"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="55"/>
-      <c r="F11" s="55"/>
-      <c r="G11" s="55"/>
-      <c r="H11" s="55"/>
-      <c r="I11" s="55"/>
-      <c r="J11" s="55"/>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="55"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="64"/>
+      <c r="J7" s="64"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
+      <c r="G8" s="64"/>
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="64"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B9" s="64"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="64"/>
+      <c r="G9" s="64"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="64"/>
+      <c r="J9" s="64"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B10" s="64"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="G10" s="64"/>
+      <c r="H10" s="64"/>
+      <c r="I10" s="64"/>
+      <c r="J10" s="64"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="64"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
+      <c r="E11" s="64"/>
+      <c r="F11" s="64"/>
+      <c r="G11" s="64"/>
+      <c r="H11" s="64"/>
+      <c r="I11" s="64"/>
+      <c r="J11" s="64"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B12" s="64"/>
+      <c r="C12" s="64"/>
+      <c r="D12" s="64"/>
+      <c r="E12" s="64"/>
+      <c r="F12" s="64"/>
+      <c r="G12" s="64"/>
+      <c r="H12" s="64"/>
+      <c r="I12" s="64"/>
+      <c r="J12" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1836,22 +1865,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:J12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="54" t="s">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B3" s="3"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -1862,42 +1891,42 @@
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="55" t="s">
+    <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
-      <c r="F6" s="55"/>
-      <c r="G6" s="55"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="55"/>
-      <c r="J6" s="55"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1908,7 +1937,7 @@
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="4"/>
       <c r="C8" s="2" t="s">
         <v>4</v>
@@ -1921,33 +1950,33 @@
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="5"/>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="58"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="D9" s="67"/>
+      <c r="E9" s="67"/>
+      <c r="F9" s="67"/>
+      <c r="G9" s="67"/>
+      <c r="H9" s="67"/>
+      <c r="I9" s="67"/>
+      <c r="J9" s="67"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="6"/>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="67" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="58"/>
-      <c r="H10" s="58"/>
-      <c r="I10" s="58"/>
-      <c r="J10" s="58"/>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="D10" s="67"/>
+      <c r="E10" s="67"/>
+      <c r="F10" s="67"/>
+      <c r="G10" s="67"/>
+      <c r="H10" s="67"/>
+      <c r="I10" s="67"/>
+      <c r="J10" s="67"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="7"/>
       <c r="C11" s="1" t="s">
         <v>7</v>
@@ -1960,18 +1989,18 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="8"/>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="67" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="58"/>
-      <c r="J12" s="58"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1989,52 +2018,52 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:P110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="6" width="18.85546875" customWidth="1"/>
-    <col min="7" max="7" width="23.42578125" customWidth="1"/>
-    <col min="8" max="8" width="13.5703125" customWidth="1"/>
-    <col min="9" max="15" width="18.85546875" customWidth="1"/>
-    <col min="16" max="16" width="64.5703125" customWidth="1"/>
+    <col min="3" max="6" width="18.88671875" customWidth="1"/>
+    <col min="7" max="7" width="23.44140625" customWidth="1"/>
+    <col min="8" max="8" width="13.5546875" customWidth="1"/>
+    <col min="9" max="15" width="18.88671875" customWidth="1"/>
+    <col min="16" max="16" width="64.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="C2" s="54" t="s">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C2" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="54"/>
-    </row>
-    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="55" t="s">
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+    </row>
+    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="55"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="55"/>
-      <c r="O4" s="55"/>
-      <c r="P4" s="55"/>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="64"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -2050,8 +2079,8 @@
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
     </row>
-    <row r="6" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="56" t="s">
+    <row r="6" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="65" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -2059,7 +2088,7 @@
       </c>
       <c r="E6" s="11">
         <f>SUM(N11:N110)</f>
-        <v>2167.5</v>
+        <v>2715</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
@@ -2073,18 +2102,18 @@
       <c r="O6" s="9"/>
       <c r="P6" s="9"/>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="C7" s="56"/>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C7" s="65"/>
       <c r="D7" s="12" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="13">
         <f>SUM(O11:O110)</f>
-        <v>2075.8333324999999</v>
+        <v>2618.3333324999999</v>
       </c>
       <c r="J7" s="14"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" s="15"/>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
@@ -2092,22 +2121,22 @@
       <c r="F9" s="16"/>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
-      <c r="I9" s="57" t="s">
+      <c r="I9" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="57"/>
+      <c r="J9" s="66"/>
       <c r="K9" s="16"/>
-      <c r="L9" s="57" t="s">
+      <c r="L9" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="M9" s="57"/>
-      <c r="N9" s="57" t="s">
+      <c r="M9" s="66"/>
+      <c r="N9" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="O9" s="57"/>
+      <c r="O9" s="66"/>
       <c r="P9" s="16"/>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" s="53" t="s">
         <v>17</v>
       </c>
@@ -2154,7 +2183,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B11" s="20">
         <v>1</v>
       </c>
@@ -2203,7 +2232,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B12" s="20">
         <v>2</v>
       </c>
@@ -2252,7 +2281,7 @@
       </c>
       <c r="P12" s="22"/>
     </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B13" s="20">
         <v>3</v>
       </c>
@@ -2303,7 +2332,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B14" s="20">
         <v>4</v>
       </c>
@@ -2353,7 +2382,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B15" s="20">
         <v>5</v>
       </c>
@@ -2381,7 +2410,7 @@
         <v>46072.5625</v>
       </c>
       <c r="K15" s="25" t="str">
-        <f t="shared" ref="K15:K46" ca="1" si="0">IF(OR(I15="",J15=""),"",IF(AND(J15&lt;&gt;"",I15&gt;=NOW()),"Planned",IF(AND(J15&lt;&gt;"",J15&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ref="K15:K25" ca="1" si="0">IF(OR(I15="",J15=""),"",IF(AND(J15&lt;&gt;"",I15&gt;=NOW()),"Planned",IF(AND(J15&lt;&gt;"",J15&lt;NOW()),"Completed","Ongoing")))</f>
         <v>Completed</v>
       </c>
       <c r="L15" s="26">
@@ -2402,7 +2431,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B16" s="20">
         <v>6</v>
       </c>
@@ -2453,7 +2482,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B17" s="20">
         <v>7</v>
       </c>
@@ -2504,7 +2533,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B18" s="20">
         <v>8</v>
       </c>
@@ -2555,7 +2584,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B19" s="20">
         <v>9</v>
       </c>
@@ -2606,7 +2635,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B20" s="20">
         <v>10</v>
       </c>
@@ -2657,7 +2686,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B21" s="20">
         <v>11</v>
       </c>
@@ -2708,7 +2737,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B22" s="20">
         <v>12</v>
       </c>
@@ -2759,7 +2788,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B23" s="20">
         <v>13</v>
       </c>
@@ -2808,7 +2837,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B24" s="20">
         <v>14</v>
       </c>
@@ -2832,7 +2861,7 @@
         <v>68</v>
       </c>
       <c r="I24" s="24">
-        <v>46101.833333333299</v>
+        <v>46101.833333333336</v>
       </c>
       <c r="J24" s="24">
         <v>46101.854166666701</v>
@@ -2859,7 +2888,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B25" s="20">
         <v>15</v>
       </c>
@@ -2910,7 +2939,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B26" s="20">
         <v>16</v>
       </c>
@@ -2958,7 +2987,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B27" s="20">
         <v>17</v>
       </c>
@@ -3007,7 +3036,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B28" s="20">
         <v>18</v>
       </c>
@@ -3056,7 +3085,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B29" s="20">
         <v>19</v>
       </c>
@@ -3105,7 +3134,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B30" s="20">
         <v>20</v>
       </c>
@@ -3154,7 +3183,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B31" s="20">
         <v>21</v>
       </c>
@@ -3203,7 +3232,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B32" s="20">
         <v>22</v>
       </c>
@@ -3252,7 +3281,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B33" s="20">
         <v>23</v>
       </c>
@@ -3301,7 +3330,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B34" s="20">
         <v>24</v>
       </c>
@@ -3350,40 +3379,40 @@
         <v>131</v>
       </c>
     </row>
-    <row r="35" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B35" s="20">
         <v>25</v>
       </c>
-      <c r="C35" s="59" t="s">
+      <c r="C35" s="54" t="s">
         <v>132</v>
       </c>
-      <c r="D35" s="60" t="s">
+      <c r="D35" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="E35" s="61" t="s">
+      <c r="E35" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="F35" s="61" t="s">
+      <c r="F35" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="G35" s="60" t="s">
+      <c r="G35" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="H35" s="61"/>
-      <c r="I35" s="62">
+      <c r="H35" s="56"/>
+      <c r="I35" s="57">
         <v>46067.458333333336</v>
       </c>
-      <c r="J35" s="62">
+      <c r="J35" s="57">
         <v>46067.583333333336</v>
       </c>
-      <c r="K35" s="63" t="str">
+      <c r="K35" s="58" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
-      <c r="L35" s="65">
+      <c r="L35" s="60">
         <v>3</v>
       </c>
-      <c r="M35" s="65">
+      <c r="M35" s="60">
         <v>3</v>
       </c>
       <c r="N35" s="25">
@@ -3394,46 +3423,46 @@
         <f>IF(ISBLANK(M35), "", M35*VLOOKUP($F35,Internal!$B$26:$C$32,2,FALSE()))</f>
         <v>75</v>
       </c>
-      <c r="P35" s="66" t="s">
+      <c r="P35" s="61" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="36" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B36" s="20">
         <v>26</v>
       </c>
-      <c r="C36" s="59" t="s">
+      <c r="C36" s="54" t="s">
         <v>133</v>
       </c>
-      <c r="D36" s="60" t="s">
+      <c r="D36" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="E36" s="61" t="s">
+      <c r="E36" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="F36" s="61" t="s">
+      <c r="F36" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="G36" s="60" t="s">
+      <c r="G36" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="H36" s="61" t="s">
+      <c r="H36" s="56" t="s">
         <v>132</v>
       </c>
-      <c r="I36" s="62">
+      <c r="I36" s="57">
         <v>46069.6875</v>
       </c>
-      <c r="J36" s="62">
+      <c r="J36" s="57">
         <v>46069.75</v>
       </c>
-      <c r="K36" s="63" t="str">
+      <c r="K36" s="58" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
-      <c r="L36" s="65">
+      <c r="L36" s="60">
         <v>2</v>
       </c>
-      <c r="M36" s="65">
+      <c r="M36" s="60">
         <v>1.5</v>
       </c>
       <c r="N36" s="25">
@@ -3444,44 +3473,44 @@
         <f>IF(ISBLANK(M36), "", M36*VLOOKUP($F36,Internal!$B$26:$C$32,2,FALSE()))</f>
         <v>37.5</v>
       </c>
-      <c r="P36" s="66" t="s">
+      <c r="P36" s="61" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B37" s="20">
         <v>27</v>
       </c>
-      <c r="C37" s="59" t="s">
+      <c r="C37" s="54" t="s">
         <v>134</v>
       </c>
-      <c r="D37" s="60" t="s">
+      <c r="D37" s="55" t="s">
         <v>30</v>
       </c>
-      <c r="E37" s="61" t="s">
+      <c r="E37" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="F37" s="61" t="s">
+      <c r="F37" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="G37" s="60" t="s">
+      <c r="G37" s="55" t="s">
         <v>48</v>
       </c>
-      <c r="H37" s="61"/>
-      <c r="I37" s="62">
+      <c r="H37" s="56"/>
+      <c r="I37" s="57">
         <v>46075.729166666664</v>
       </c>
-      <c r="J37" s="62">
+      <c r="J37" s="57">
         <v>46075.8125</v>
       </c>
-      <c r="K37" s="63" t="str">
+      <c r="K37" s="58" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
-      <c r="L37" s="65">
+      <c r="L37" s="60">
         <v>2</v>
       </c>
-      <c r="M37" s="65">
+      <c r="M37" s="60">
         <v>2</v>
       </c>
       <c r="N37" s="25">
@@ -3492,46 +3521,46 @@
         <f>IF(ISBLANK(M37), "", M37*VLOOKUP($F37,Internal!$B$26:$C$32,2,FALSE()))</f>
         <v>100</v>
       </c>
-      <c r="P37" s="66" t="s">
+      <c r="P37" s="61" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B38" s="20">
         <v>28</v>
       </c>
-      <c r="C38" s="59" t="s">
+      <c r="C38" s="54" t="s">
         <v>135</v>
       </c>
-      <c r="D38" s="60" t="s">
+      <c r="D38" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="E38" s="61" t="s">
+      <c r="E38" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="F38" s="61" t="s">
+      <c r="F38" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="G38" s="60" t="s">
+      <c r="G38" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="H38" s="61" t="s">
+      <c r="H38" s="56" t="s">
         <v>133</v>
       </c>
-      <c r="I38" s="62">
+      <c r="I38" s="57">
         <v>46078.625</v>
       </c>
-      <c r="J38" s="62">
+      <c r="J38" s="57">
         <v>46078.71875</v>
       </c>
-      <c r="K38" s="63" t="str">
+      <c r="K38" s="58" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
-      <c r="L38" s="65">
+      <c r="L38" s="60">
         <v>2</v>
       </c>
-      <c r="M38" s="65">
+      <c r="M38" s="60">
         <v>2.25</v>
       </c>
       <c r="N38" s="25">
@@ -3542,46 +3571,46 @@
         <f>IF(ISBLANK(M38), "", M38*VLOOKUP($F38,Internal!$B$26:$C$32,2,FALSE()))</f>
         <v>56.25</v>
       </c>
-      <c r="P38" s="66" t="s">
+      <c r="P38" s="61" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B39" s="20">
         <v>29</v>
       </c>
-      <c r="C39" s="59" t="s">
+      <c r="C39" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="D39" s="60" t="s">
+      <c r="D39" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="E39" s="61" t="s">
+      <c r="E39" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="F39" s="61" t="s">
+      <c r="F39" s="56" t="s">
         <v>37</v>
       </c>
-      <c r="G39" s="60" t="s">
+      <c r="G39" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="H39" s="61" t="s">
+      <c r="H39" s="56" t="s">
         <v>135</v>
       </c>
-      <c r="I39" s="62">
+      <c r="I39" s="57">
         <v>46083.458333333336</v>
       </c>
-      <c r="J39" s="62">
+      <c r="J39" s="57">
         <v>46083.604166666664</v>
       </c>
-      <c r="K39" s="63" t="str">
+      <c r="K39" s="58" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
-      <c r="L39" s="65">
+      <c r="L39" s="60">
         <v>3</v>
       </c>
-      <c r="M39" s="65">
+      <c r="M39" s="60">
         <v>3.5</v>
       </c>
       <c r="N39" s="25">
@@ -3592,46 +3621,46 @@
         <f>IF(ISBLANK(M39), "", M39*VLOOKUP($F39,Internal!$B$26:$C$32,2,FALSE()))</f>
         <v>87.5</v>
       </c>
-      <c r="P39" s="66" t="s">
+      <c r="P39" s="61" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B40" s="20">
         <v>30</v>
       </c>
-      <c r="C40" s="59" t="s">
+      <c r="C40" s="54" t="s">
         <v>137</v>
       </c>
-      <c r="D40" s="60" t="s">
+      <c r="D40" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="E40" s="61" t="s">
+      <c r="E40" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="F40" s="61" t="s">
+      <c r="F40" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="G40" s="60" t="s">
+      <c r="G40" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="H40" s="61" t="s">
+      <c r="H40" s="56" t="s">
         <v>136</v>
       </c>
-      <c r="I40" s="62">
+      <c r="I40" s="57">
         <v>46084.5</v>
       </c>
-      <c r="J40" s="62">
+      <c r="J40" s="57">
         <v>46084.5625</v>
       </c>
-      <c r="K40" s="63" t="str">
+      <c r="K40" s="58" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
-      <c r="L40" s="65">
+      <c r="L40" s="60">
         <v>2</v>
       </c>
-      <c r="M40" s="65">
+      <c r="M40" s="60">
         <v>1.5</v>
       </c>
       <c r="N40" s="25">
@@ -3642,46 +3671,46 @@
         <f>IF(ISBLANK(M40), "", M40*VLOOKUP($F40,Internal!$B$26:$C$32,2,FALSE()))</f>
         <v>45</v>
       </c>
-      <c r="P40" s="66" t="s">
+      <c r="P40" s="61" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B41" s="20">
         <v>31</v>
       </c>
-      <c r="C41" s="59" t="s">
+      <c r="C41" s="54" t="s">
         <v>138</v>
       </c>
-      <c r="D41" s="60" t="s">
+      <c r="D41" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="E41" s="61" t="s">
+      <c r="E41" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="F41" s="67" t="s">
+      <c r="F41" s="62" t="s">
         <v>37</v>
       </c>
-      <c r="G41" s="60" t="s">
+      <c r="G41" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="H41" s="61" t="s">
+      <c r="H41" s="56" t="s">
         <v>136</v>
       </c>
-      <c r="I41" s="62">
+      <c r="I41" s="57">
         <v>46100.5</v>
       </c>
-      <c r="J41" s="64">
+      <c r="J41" s="59">
         <v>46100.572916666664</v>
       </c>
-      <c r="K41" s="63" t="str">
+      <c r="K41" s="58" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
-      <c r="L41" s="65">
+      <c r="L41" s="60">
         <v>1.5</v>
       </c>
-      <c r="M41" s="65">
+      <c r="M41" s="60">
         <v>1.75</v>
       </c>
       <c r="N41" s="25">
@@ -3692,46 +3721,46 @@
         <f>IF(ISBLANK(M41), "", M41*VLOOKUP($F41,Internal!$B$26:$C$32,2,FALSE()))</f>
         <v>43.75</v>
       </c>
-      <c r="P41" s="66" t="s">
+      <c r="P41" s="61" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="42" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="20">
         <v>32</v>
       </c>
-      <c r="C42" s="59" t="s">
+      <c r="C42" s="54" t="s">
         <v>139</v>
       </c>
-      <c r="D42" s="60" t="s">
+      <c r="D42" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="E42" s="61" t="s">
+      <c r="E42" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="F42" s="61" t="s">
+      <c r="F42" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="G42" s="60" t="s">
+      <c r="G42" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="H42" s="61" t="s">
+      <c r="H42" s="56" t="s">
         <v>138</v>
       </c>
-      <c r="I42" s="62">
+      <c r="I42" s="57">
         <v>46100.59375</v>
       </c>
-      <c r="J42" s="62">
+      <c r="J42" s="57">
         <v>46100.697916666664</v>
       </c>
-      <c r="K42" s="63" t="str">
+      <c r="K42" s="58" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
-      <c r="L42" s="65">
+      <c r="L42" s="60">
         <v>3</v>
       </c>
-      <c r="M42" s="65">
+      <c r="M42" s="60">
         <v>2.5</v>
       </c>
       <c r="N42" s="25">
@@ -3742,46 +3771,46 @@
         <f>IF(ISBLANK(M42), "", M42*VLOOKUP($F42,Internal!$B$26:$C$32,2,FALSE()))</f>
         <v>75</v>
       </c>
-      <c r="P42" s="66" t="s">
+      <c r="P42" s="61" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="43" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B43" s="20">
         <v>33</v>
       </c>
-      <c r="C43" s="59" t="s">
+      <c r="C43" s="54" t="s">
         <v>140</v>
       </c>
-      <c r="D43" s="60" t="s">
+      <c r="D43" s="55" t="s">
         <v>55</v>
       </c>
-      <c r="E43" s="61" t="s">
+      <c r="E43" s="56" t="s">
         <v>91</v>
       </c>
-      <c r="F43" s="61" t="s">
+      <c r="F43" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="G43" s="60" t="s">
+      <c r="G43" s="55" t="s">
         <v>63</v>
       </c>
-      <c r="H43" s="61" t="s">
+      <c r="H43" s="56" t="s">
         <v>138</v>
       </c>
-      <c r="I43" s="62">
+      <c r="I43" s="57">
         <v>46101.4375</v>
       </c>
-      <c r="J43" s="62">
+      <c r="J43" s="57">
         <v>46101.520833333336</v>
       </c>
-      <c r="K43" s="63" t="str">
+      <c r="K43" s="58" t="str">
         <f t="shared" ca="1" si="1"/>
         <v>Completed</v>
       </c>
-      <c r="L43" s="65">
+      <c r="L43" s="60">
         <v>2</v>
       </c>
-      <c r="M43" s="65">
+      <c r="M43" s="60">
         <v>2</v>
       </c>
       <c r="N43" s="25">
@@ -3792,266 +3821,399 @@
         <f>IF(ISBLANK(M43), "", M43*VLOOKUP($F43,Internal!$B$26:$C$32,2,FALSE()))</f>
         <v>60</v>
       </c>
-      <c r="P43" s="66" t="s">
+      <c r="P43" s="61" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="44" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B44" s="20">
         <v>34</v>
       </c>
-      <c r="C44" s="21" t="str">
-        <f>IF(ISBLANK(D44), "", _xlfn.CONCAT("T", TEXT(B44, "0000"), "/", VLOOKUP(D44, Internal!$B$35:C$39, 2, FALSE()), IF(OR(D44="QA", D44="Revision"), _xlfn.CONCAT("/", H44), "")))</f>
-        <v/>
-      </c>
-      <c r="D44" s="22"/>
-      <c r="E44" s="23"/>
-      <c r="F44" s="23"/>
-      <c r="G44" s="22"/>
-      <c r="H44" s="23"/>
-      <c r="I44" s="24"/>
-      <c r="J44" s="24"/>
-      <c r="K44" s="25" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L44" s="26"/>
-      <c r="M44" s="26"/>
-      <c r="N44" s="25" t="str">
+      <c r="C44" s="54" t="s">
+        <v>151</v>
+      </c>
+      <c r="D44" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E44" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="F44" s="56" t="s">
+        <v>37</v>
+      </c>
+      <c r="G44" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="H44" s="56"/>
+      <c r="I44" s="57">
+        <v>46065.375</v>
+      </c>
+      <c r="J44" s="57">
+        <v>46065.5</v>
+      </c>
+      <c r="K44" s="58" t="str">
+        <f t="shared" ref="K44:K51" ca="1" si="2">IF(OR(I44="",J44=""),"",IF(AND(J44&lt;&gt;"",I44&gt;=NOW()),"Planned",IF(AND(J44&lt;&gt;"",J44&lt;NOW()),"Completed","Ongoing")))</f>
+        <v>Completed</v>
+      </c>
+      <c r="L44" s="60">
+        <v>3</v>
+      </c>
+      <c r="M44" s="60">
+        <v>3</v>
+      </c>
+      <c r="N44" s="25">
         <f>IF(ISBLANK(L44), "", L44*VLOOKUP($F44,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="O44" s="25" t="str">
+        <v>75</v>
+      </c>
+      <c r="O44" s="25">
         <f>IF(ISBLANK(M44), "", M44*VLOOKUP($F44,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="P44" s="22"/>
-    </row>
-    <row r="45" spans="2:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>75</v>
+      </c>
+      <c r="P44" s="61" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B45" s="20">
         <v>35</v>
       </c>
-      <c r="C45" s="21" t="str">
-        <f>IF(ISBLANK(D45), "", _xlfn.CONCAT("T", TEXT(B45, "0000"), "/", VLOOKUP(D45, Internal!$B$35:C$39, 2, FALSE()), IF(OR(D45="QA", D45="Revision"), _xlfn.CONCAT("/", H45), "")))</f>
-        <v/>
-      </c>
-      <c r="D45" s="22"/>
-      <c r="E45" s="23"/>
-      <c r="F45" s="23"/>
-      <c r="G45" s="22"/>
-      <c r="H45" s="23"/>
-      <c r="I45" s="24"/>
-      <c r="J45" s="24"/>
-      <c r="K45" s="25" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L45" s="26"/>
-      <c r="M45" s="26"/>
-      <c r="N45" s="25" t="str">
+      <c r="C45" s="54" t="s">
+        <v>152</v>
+      </c>
+      <c r="D45" s="55" t="s">
+        <v>30</v>
+      </c>
+      <c r="E45" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="F45" s="56" t="s">
+        <v>45</v>
+      </c>
+      <c r="G45" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="H45" s="56"/>
+      <c r="I45" s="57">
+        <v>46075.729166666664</v>
+      </c>
+      <c r="J45" s="57">
+        <v>46075.8125</v>
+      </c>
+      <c r="K45" s="58" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>Completed</v>
+      </c>
+      <c r="L45" s="60">
+        <v>2</v>
+      </c>
+      <c r="M45" s="60">
+        <v>2</v>
+      </c>
+      <c r="N45" s="25">
         <f>IF(ISBLANK(L45), "", L45*VLOOKUP($F45,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="O45" s="25" t="str">
+        <v>100</v>
+      </c>
+      <c r="O45" s="25">
         <f>IF(ISBLANK(M45), "", M45*VLOOKUP($F45,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="P45" s="22"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="P45" s="61" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B46" s="20">
         <v>36</v>
       </c>
-      <c r="C46" s="21" t="str">
-        <f>IF(ISBLANK(D46), "", _xlfn.CONCAT("T", TEXT(B46, "0000"), "/", VLOOKUP(D46, Internal!$B$35:C$39, 2, FALSE()), IF(OR(D46="QA", D46="Revision"), _xlfn.CONCAT("/", H46), "")))</f>
-        <v/>
-      </c>
-      <c r="D46" s="22"/>
-      <c r="E46" s="23"/>
-      <c r="F46" s="23"/>
-      <c r="G46" s="22"/>
-      <c r="H46" s="23"/>
-      <c r="I46" s="24"/>
-      <c r="J46" s="24"/>
-      <c r="K46" s="25" t="str">
-        <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L46" s="26"/>
-      <c r="M46" s="26"/>
-      <c r="N46" s="25" t="str">
+      <c r="C46" s="54" t="s">
+        <v>153</v>
+      </c>
+      <c r="D46" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="E46" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="F46" s="56" t="s">
+        <v>37</v>
+      </c>
+      <c r="G46" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="H46" s="56"/>
+      <c r="I46" s="57">
+        <v>46078.625</v>
+      </c>
+      <c r="J46" s="57">
+        <v>46078.71875</v>
+      </c>
+      <c r="K46" s="58" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>Completed</v>
+      </c>
+      <c r="L46" s="60">
+        <v>2</v>
+      </c>
+      <c r="M46" s="60">
+        <v>2.25</v>
+      </c>
+      <c r="N46" s="25">
         <f>IF(ISBLANK(L46), "", L46*VLOOKUP($F46,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="O46" s="25" t="str">
+        <v>50</v>
+      </c>
+      <c r="O46" s="25">
         <f>IF(ISBLANK(M46), "", M46*VLOOKUP($F46,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="P46" s="22"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.25">
+        <v>56.25</v>
+      </c>
+      <c r="P46" s="61" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="20">
         <v>37</v>
       </c>
-      <c r="C47" s="21" t="str">
-        <f>IF(ISBLANK(D47), "", _xlfn.CONCAT("T", TEXT(B47, "0000"), "/", VLOOKUP(D47, Internal!$B$35:C$39, 2, FALSE()), IF(OR(D47="QA", D47="Revision"), _xlfn.CONCAT("/", H47), "")))</f>
-        <v/>
-      </c>
-      <c r="D47" s="22"/>
-      <c r="E47" s="23"/>
-      <c r="F47" s="23"/>
-      <c r="G47" s="22"/>
-      <c r="H47" s="23"/>
-      <c r="I47" s="24"/>
-      <c r="J47" s="24"/>
-      <c r="K47" s="25" t="str">
-        <f t="shared" ref="K47:K78" ca="1" si="2">IF(OR(I47="",J47=""),"",IF(AND(J47&lt;&gt;"",I47&gt;=NOW()),"Planned",IF(AND(J47&lt;&gt;"",J47&lt;NOW()),"Completed","Ongoing")))</f>
-        <v/>
-      </c>
-      <c r="L47" s="26"/>
-      <c r="M47" s="26"/>
-      <c r="N47" s="25" t="str">
+      <c r="C47" s="54" t="s">
+        <v>154</v>
+      </c>
+      <c r="D47" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="E47" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="F47" s="56" t="s">
+        <v>37</v>
+      </c>
+      <c r="G47" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="H47" s="56"/>
+      <c r="I47" s="57">
+        <v>46083.458333333336</v>
+      </c>
+      <c r="J47" s="57">
+        <v>46083.604166666664</v>
+      </c>
+      <c r="K47" s="58" t="str">
+        <f t="shared" ca="1" si="2"/>
+        <v>Completed</v>
+      </c>
+      <c r="L47" s="60">
+        <v>3</v>
+      </c>
+      <c r="M47" s="60">
+        <v>3.5</v>
+      </c>
+      <c r="N47" s="25">
         <f>IF(ISBLANK(L47), "", L47*VLOOKUP($F47,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="O47" s="25" t="str">
+        <v>75</v>
+      </c>
+      <c r="O47" s="25">
         <f>IF(ISBLANK(M47), "", M47*VLOOKUP($F47,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="P47" s="22"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.25">
+        <v>87.5</v>
+      </c>
+      <c r="P47" s="61" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="48" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B48" s="20">
         <v>38</v>
       </c>
-      <c r="C48" s="21" t="str">
-        <f>IF(ISBLANK(D48), "", _xlfn.CONCAT("T", TEXT(B48, "0000"), "/", VLOOKUP(D48, Internal!$B$35:C$39, 2, FALSE()), IF(OR(D48="QA", D48="Revision"), _xlfn.CONCAT("/", H48), "")))</f>
-        <v/>
-      </c>
-      <c r="D48" s="22"/>
-      <c r="E48" s="23"/>
-      <c r="F48" s="23"/>
-      <c r="G48" s="22"/>
-      <c r="H48" s="23"/>
-      <c r="I48" s="24"/>
-      <c r="J48" s="24"/>
-      <c r="K48" s="25" t="str">
+      <c r="C48" s="54" t="s">
+        <v>155</v>
+      </c>
+      <c r="D48" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="E48" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="F48" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="G48" s="55" t="s">
+        <v>57</v>
+      </c>
+      <c r="H48" s="56"/>
+      <c r="I48" s="57">
+        <v>46084.5</v>
+      </c>
+      <c r="J48" s="57">
+        <v>46084.5625</v>
+      </c>
+      <c r="K48" s="58" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="L48" s="26"/>
-      <c r="M48" s="26"/>
-      <c r="N48" s="25" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L48" s="60">
+        <v>2</v>
+      </c>
+      <c r="M48" s="60">
+        <v>1.5</v>
+      </c>
+      <c r="N48" s="25">
         <f>IF(ISBLANK(L48), "", L48*VLOOKUP($F48,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="O48" s="25" t="str">
+        <v>60</v>
+      </c>
+      <c r="O48" s="25">
         <f>IF(ISBLANK(M48), "", M48*VLOOKUP($F48,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="P48" s="22"/>
-    </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="P48" s="61" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="49" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B49" s="20">
         <v>39</v>
       </c>
-      <c r="C49" s="21" t="str">
-        <f>IF(ISBLANK(D49), "", _xlfn.CONCAT("T", TEXT(B49, "0000"), "/", VLOOKUP(D49, Internal!$B$35:C$39, 2, FALSE()), IF(OR(D49="QA", D49="Revision"), _xlfn.CONCAT("/", H49), "")))</f>
-        <v/>
-      </c>
-      <c r="D49" s="22"/>
-      <c r="E49" s="23"/>
-      <c r="F49" s="23"/>
-      <c r="G49" s="22"/>
-      <c r="H49" s="23"/>
-      <c r="I49" s="24"/>
-      <c r="J49" s="24"/>
-      <c r="K49" s="25" t="str">
+      <c r="C49" s="54" t="s">
+        <v>156</v>
+      </c>
+      <c r="D49" s="55" t="s">
+        <v>35</v>
+      </c>
+      <c r="E49" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="F49" s="62" t="s">
+        <v>37</v>
+      </c>
+      <c r="G49" s="55" t="s">
+        <v>42</v>
+      </c>
+      <c r="H49" s="56"/>
+      <c r="I49" s="57">
+        <v>46100.5</v>
+      </c>
+      <c r="J49" s="59">
+        <v>46100.572916666664</v>
+      </c>
+      <c r="K49" s="58" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="L49" s="26"/>
-      <c r="M49" s="26"/>
-      <c r="N49" s="25" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L49" s="60">
+        <v>1.5</v>
+      </c>
+      <c r="M49" s="60">
+        <v>1.75</v>
+      </c>
+      <c r="N49" s="25">
         <f>IF(ISBLANK(L49), "", L49*VLOOKUP($F49,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="O49" s="25" t="str">
+        <v>37.5</v>
+      </c>
+      <c r="O49" s="25">
         <f>IF(ISBLANK(M49), "", M49*VLOOKUP($F49,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="P49" s="22"/>
-    </row>
-    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
+        <v>43.75</v>
+      </c>
+      <c r="P49" s="61" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="50" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B50" s="20">
         <v>40</v>
       </c>
-      <c r="C50" s="21" t="str">
-        <f>IF(ISBLANK(D50), "", _xlfn.CONCAT("T", TEXT(B50, "0000"), "/", VLOOKUP(D50, Internal!$B$35:C$39, 2, FALSE()), IF(OR(D50="QA", D50="Revision"), _xlfn.CONCAT("/", H50), "")))</f>
-        <v/>
-      </c>
-      <c r="D50" s="22"/>
-      <c r="E50" s="23"/>
-      <c r="F50" s="23"/>
-      <c r="G50" s="22"/>
-      <c r="H50" s="23"/>
-      <c r="I50" s="24"/>
-      <c r="J50" s="24"/>
-      <c r="K50" s="25" t="str">
+      <c r="C50" s="54" t="s">
+        <v>157</v>
+      </c>
+      <c r="D50" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="E50" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="F50" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="G50" s="55" t="s">
+        <v>57</v>
+      </c>
+      <c r="H50" s="56"/>
+      <c r="I50" s="57">
+        <v>46100.59375</v>
+      </c>
+      <c r="J50" s="57">
+        <v>46100.697916666664</v>
+      </c>
+      <c r="K50" s="58" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="L50" s="26"/>
-      <c r="M50" s="26"/>
-      <c r="N50" s="25" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L50" s="60">
+        <v>3</v>
+      </c>
+      <c r="M50" s="60">
+        <v>2.5</v>
+      </c>
+      <c r="N50" s="25">
         <f>IF(ISBLANK(L50), "", L50*VLOOKUP($F50,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="O50" s="25" t="str">
+        <v>90</v>
+      </c>
+      <c r="O50" s="25">
         <f>IF(ISBLANK(M50), "", M50*VLOOKUP($F50,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="P50" s="22"/>
-    </row>
-    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="P50" s="61" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="51" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B51" s="20">
         <v>41</v>
       </c>
-      <c r="C51" s="21" t="str">
-        <f>IF(ISBLANK(D51), "", _xlfn.CONCAT("T", TEXT(B51, "0000"), "/", VLOOKUP(D51, Internal!$B$35:C$39, 2, FALSE()), IF(OR(D51="QA", D51="Revision"), _xlfn.CONCAT("/", H51), "")))</f>
-        <v/>
-      </c>
-      <c r="D51" s="22"/>
-      <c r="E51" s="23"/>
-      <c r="F51" s="23"/>
-      <c r="G51" s="22"/>
-      <c r="H51" s="23"/>
-      <c r="I51" s="24"/>
-      <c r="J51" s="24"/>
-      <c r="K51" s="25" t="str">
+      <c r="C51" s="54" t="s">
+        <v>158</v>
+      </c>
+      <c r="D51" s="55" t="s">
+        <v>55</v>
+      </c>
+      <c r="E51" s="56" t="s">
+        <v>36</v>
+      </c>
+      <c r="F51" s="56" t="s">
+        <v>56</v>
+      </c>
+      <c r="G51" s="55" t="s">
+        <v>63</v>
+      </c>
+      <c r="H51" s="56"/>
+      <c r="I51" s="57">
+        <v>46101.4375</v>
+      </c>
+      <c r="J51" s="57">
+        <v>46101.520833333336</v>
+      </c>
+      <c r="K51" s="58" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v/>
-      </c>
-      <c r="L51" s="26"/>
-      <c r="M51" s="26"/>
-      <c r="N51" s="25" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L51" s="60">
+        <v>2</v>
+      </c>
+      <c r="M51" s="60">
+        <v>2</v>
+      </c>
+      <c r="N51" s="25">
         <f>IF(ISBLANK(L51), "", L51*VLOOKUP($F51,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="O51" s="25" t="str">
+        <v>60</v>
+      </c>
+      <c r="O51" s="25">
         <f>IF(ISBLANK(M51), "", M51*VLOOKUP($F51,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="P51" s="22"/>
-    </row>
-    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
+        <v>60</v>
+      </c>
+      <c r="P51" s="61" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B52" s="20">
         <v>42</v>
       </c>
-      <c r="C52" s="21" t="str">
-        <f>IF(ISBLANK(D52), "", _xlfn.CONCAT("T", TEXT(B52, "0000"), "/", VLOOKUP(D52, Internal!$B$35:C$39, 2, FALSE()), IF(OR(D52="QA", D52="Revision"), _xlfn.CONCAT("/", H52), "")))</f>
-        <v/>
-      </c>
+      <c r="C52" s="21"/>
       <c r="D52" s="22"/>
       <c r="E52" s="23"/>
       <c r="F52" s="23"/>
@@ -4060,7 +4222,7 @@
       <c r="I52" s="24"/>
       <c r="J52" s="24"/>
       <c r="K52" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ref="K52" ca="1" si="3">IF(OR(I52="",J52=""),"",IF(AND(J52&lt;&gt;"",I52&gt;=NOW()),"Planned",IF(AND(J52&lt;&gt;"",J52&lt;NOW()),"Completed","Ongoing")))</f>
         <v/>
       </c>
       <c r="L52" s="26"/>
@@ -4075,7 +4237,7 @@
       </c>
       <c r="P52" s="22"/>
     </row>
-    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B53" s="20">
         <v>43</v>
       </c>
@@ -4091,7 +4253,7 @@
       <c r="I53" s="24"/>
       <c r="J53" s="24"/>
       <c r="K53" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ref="K53:K78" ca="1" si="4">IF(OR(I53="",J53=""),"",IF(AND(J53&lt;&gt;"",I53&gt;=NOW()),"Planned",IF(AND(J53&lt;&gt;"",J53&lt;NOW()),"Completed","Ongoing")))</f>
         <v/>
       </c>
       <c r="L53" s="26"/>
@@ -4106,7 +4268,7 @@
       </c>
       <c r="P53" s="22"/>
     </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B54" s="20">
         <v>44</v>
       </c>
@@ -4122,7 +4284,7 @@
       <c r="I54" s="24"/>
       <c r="J54" s="24"/>
       <c r="K54" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="L54" s="26"/>
@@ -4137,7 +4299,7 @@
       </c>
       <c r="P54" s="22"/>
     </row>
-    <row r="55" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B55" s="20">
         <v>45</v>
       </c>
@@ -4153,7 +4315,7 @@
       <c r="I55" s="24"/>
       <c r="J55" s="24"/>
       <c r="K55" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="L55" s="26"/>
@@ -4168,7 +4330,7 @@
       </c>
       <c r="P55" s="22"/>
     </row>
-    <row r="56" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B56" s="20">
         <v>46</v>
       </c>
@@ -4184,7 +4346,7 @@
       <c r="I56" s="24"/>
       <c r="J56" s="24"/>
       <c r="K56" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="L56" s="26"/>
@@ -4199,7 +4361,7 @@
       </c>
       <c r="P56" s="22"/>
     </row>
-    <row r="57" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="20">
         <v>47</v>
       </c>
@@ -4215,7 +4377,7 @@
       <c r="I57" s="24"/>
       <c r="J57" s="24"/>
       <c r="K57" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="L57" s="26"/>
@@ -4230,7 +4392,7 @@
       </c>
       <c r="P57" s="22"/>
     </row>
-    <row r="58" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B58" s="20">
         <v>48</v>
       </c>
@@ -4246,7 +4408,7 @@
       <c r="I58" s="24"/>
       <c r="J58" s="24"/>
       <c r="K58" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="L58" s="26"/>
@@ -4261,7 +4423,7 @@
       </c>
       <c r="P58" s="22"/>
     </row>
-    <row r="59" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B59" s="20">
         <v>49</v>
       </c>
@@ -4277,7 +4439,7 @@
       <c r="I59" s="24"/>
       <c r="J59" s="24"/>
       <c r="K59" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="L59" s="26"/>
@@ -4292,7 +4454,7 @@
       </c>
       <c r="P59" s="22"/>
     </row>
-    <row r="60" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B60" s="20">
         <v>50</v>
       </c>
@@ -4308,7 +4470,7 @@
       <c r="I60" s="24"/>
       <c r="J60" s="24"/>
       <c r="K60" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="L60" s="26"/>
@@ -4323,7 +4485,7 @@
       </c>
       <c r="P60" s="22"/>
     </row>
-    <row r="61" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B61" s="20">
         <v>51</v>
       </c>
@@ -4339,7 +4501,7 @@
       <c r="I61" s="24"/>
       <c r="J61" s="24"/>
       <c r="K61" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="L61" s="26"/>
@@ -4354,7 +4516,7 @@
       </c>
       <c r="P61" s="22"/>
     </row>
-    <row r="62" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B62" s="20">
         <v>52</v>
       </c>
@@ -4370,7 +4532,7 @@
       <c r="I62" s="24"/>
       <c r="J62" s="24"/>
       <c r="K62" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="L62" s="26"/>
@@ -4385,7 +4547,7 @@
       </c>
       <c r="P62" s="22"/>
     </row>
-    <row r="63" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B63" s="20">
         <v>53</v>
       </c>
@@ -4401,7 +4563,7 @@
       <c r="I63" s="24"/>
       <c r="J63" s="24"/>
       <c r="K63" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="L63" s="26"/>
@@ -4416,7 +4578,7 @@
       </c>
       <c r="P63" s="22"/>
     </row>
-    <row r="64" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B64" s="20">
         <v>54</v>
       </c>
@@ -4432,7 +4594,7 @@
       <c r="I64" s="24"/>
       <c r="J64" s="24"/>
       <c r="K64" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="L64" s="26"/>
@@ -4447,7 +4609,7 @@
       </c>
       <c r="P64" s="22"/>
     </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B65" s="20">
         <v>55</v>
       </c>
@@ -4463,7 +4625,7 @@
       <c r="I65" s="24"/>
       <c r="J65" s="24"/>
       <c r="K65" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="L65" s="26"/>
@@ -4478,7 +4640,7 @@
       </c>
       <c r="P65" s="22"/>
     </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B66" s="20">
         <v>56</v>
       </c>
@@ -4494,7 +4656,7 @@
       <c r="I66" s="24"/>
       <c r="J66" s="24"/>
       <c r="K66" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="L66" s="26"/>
@@ -4509,7 +4671,7 @@
       </c>
       <c r="P66" s="22"/>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B67" s="20">
         <v>57</v>
       </c>
@@ -4525,7 +4687,7 @@
       <c r="I67" s="24"/>
       <c r="J67" s="24"/>
       <c r="K67" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="L67" s="26"/>
@@ -4540,7 +4702,7 @@
       </c>
       <c r="P67" s="22"/>
     </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B68" s="20">
         <v>58</v>
       </c>
@@ -4556,7 +4718,7 @@
       <c r="I68" s="24"/>
       <c r="J68" s="24"/>
       <c r="K68" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="L68" s="26"/>
@@ -4571,7 +4733,7 @@
       </c>
       <c r="P68" s="22"/>
     </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B69" s="20">
         <v>59</v>
       </c>
@@ -4587,7 +4749,7 @@
       <c r="I69" s="24"/>
       <c r="J69" s="24"/>
       <c r="K69" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="L69" s="26"/>
@@ -4602,7 +4764,7 @@
       </c>
       <c r="P69" s="22"/>
     </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B70" s="20">
         <v>60</v>
       </c>
@@ -4618,7 +4780,7 @@
       <c r="I70" s="24"/>
       <c r="J70" s="24"/>
       <c r="K70" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="L70" s="26"/>
@@ -4633,7 +4795,7 @@
       </c>
       <c r="P70" s="22"/>
     </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B71" s="20">
         <v>61</v>
       </c>
@@ -4649,7 +4811,7 @@
       <c r="I71" s="24"/>
       <c r="J71" s="24"/>
       <c r="K71" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="L71" s="26"/>
@@ -4664,7 +4826,7 @@
       </c>
       <c r="P71" s="22"/>
     </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B72" s="20">
         <v>62</v>
       </c>
@@ -4680,7 +4842,7 @@
       <c r="I72" s="24"/>
       <c r="J72" s="24"/>
       <c r="K72" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="L72" s="26"/>
@@ -4695,7 +4857,7 @@
       </c>
       <c r="P72" s="22"/>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B73" s="20">
         <v>63</v>
       </c>
@@ -4711,7 +4873,7 @@
       <c r="I73" s="24"/>
       <c r="J73" s="24"/>
       <c r="K73" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="L73" s="26"/>
@@ -4726,7 +4888,7 @@
       </c>
       <c r="P73" s="22"/>
     </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B74" s="20">
         <v>64</v>
       </c>
@@ -4742,7 +4904,7 @@
       <c r="I74" s="24"/>
       <c r="J74" s="24"/>
       <c r="K74" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="L74" s="26"/>
@@ -4757,7 +4919,7 @@
       </c>
       <c r="P74" s="22"/>
     </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B75" s="20">
         <v>65</v>
       </c>
@@ -4773,7 +4935,7 @@
       <c r="I75" s="24"/>
       <c r="J75" s="24"/>
       <c r="K75" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="L75" s="26"/>
@@ -4788,7 +4950,7 @@
       </c>
       <c r="P75" s="22"/>
     </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B76" s="20">
         <v>66</v>
       </c>
@@ -4804,7 +4966,7 @@
       <c r="I76" s="24"/>
       <c r="J76" s="24"/>
       <c r="K76" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="L76" s="26"/>
@@ -4819,7 +4981,7 @@
       </c>
       <c r="P76" s="22"/>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B77" s="20">
         <v>67</v>
       </c>
@@ -4835,7 +4997,7 @@
       <c r="I77" s="24"/>
       <c r="J77" s="24"/>
       <c r="K77" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="L77" s="26"/>
@@ -4850,7 +5012,7 @@
       </c>
       <c r="P77" s="22"/>
     </row>
-    <row r="78" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B78" s="20">
         <v>68</v>
       </c>
@@ -4866,7 +5028,7 @@
       <c r="I78" s="24"/>
       <c r="J78" s="24"/>
       <c r="K78" s="25" t="str">
-        <f t="shared" ca="1" si="2"/>
+        <f t="shared" ca="1" si="4"/>
         <v/>
       </c>
       <c r="L78" s="26"/>
@@ -4881,7 +5043,7 @@
       </c>
       <c r="P78" s="22"/>
     </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B79" s="20">
         <v>69</v>
       </c>
@@ -4897,7 +5059,7 @@
       <c r="I79" s="24"/>
       <c r="J79" s="24"/>
       <c r="K79" s="25" t="str">
-        <f t="shared" ref="K79:K110" ca="1" si="3">IF(OR(I79="",J79=""),"",IF(AND(J79&lt;&gt;"",I79&gt;=NOW()),"Planned",IF(AND(J79&lt;&gt;"",J79&lt;NOW()),"Completed","Ongoing")))</f>
+        <f t="shared" ref="K79:K110" ca="1" si="5">IF(OR(I79="",J79=""),"",IF(AND(J79&lt;&gt;"",I79&gt;=NOW()),"Planned",IF(AND(J79&lt;&gt;"",J79&lt;NOW()),"Completed","Ongoing")))</f>
         <v/>
       </c>
       <c r="L79" s="26"/>
@@ -4912,7 +5074,7 @@
       </c>
       <c r="P79" s="22"/>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B80" s="20">
         <v>70</v>
       </c>
@@ -4928,7 +5090,7 @@
       <c r="I80" s="24"/>
       <c r="J80" s="24"/>
       <c r="K80" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L80" s="26"/>
@@ -4943,7 +5105,7 @@
       </c>
       <c r="P80" s="22"/>
     </row>
-    <row r="81" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B81" s="20">
         <v>71</v>
       </c>
@@ -4959,7 +5121,7 @@
       <c r="I81" s="24"/>
       <c r="J81" s="24"/>
       <c r="K81" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L81" s="26"/>
@@ -4974,7 +5136,7 @@
       </c>
       <c r="P81" s="22"/>
     </row>
-    <row r="82" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B82" s="20">
         <v>72</v>
       </c>
@@ -4990,7 +5152,7 @@
       <c r="I82" s="24"/>
       <c r="J82" s="24"/>
       <c r="K82" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L82" s="26"/>
@@ -5005,7 +5167,7 @@
       </c>
       <c r="P82" s="22"/>
     </row>
-    <row r="83" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B83" s="20">
         <v>73</v>
       </c>
@@ -5021,7 +5183,7 @@
       <c r="I83" s="24"/>
       <c r="J83" s="24"/>
       <c r="K83" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L83" s="26"/>
@@ -5036,7 +5198,7 @@
       </c>
       <c r="P83" s="22"/>
     </row>
-    <row r="84" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B84" s="20">
         <v>74</v>
       </c>
@@ -5052,7 +5214,7 @@
       <c r="I84" s="24"/>
       <c r="J84" s="24"/>
       <c r="K84" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L84" s="26"/>
@@ -5067,7 +5229,7 @@
       </c>
       <c r="P84" s="22"/>
     </row>
-    <row r="85" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B85" s="20">
         <v>75</v>
       </c>
@@ -5083,7 +5245,7 @@
       <c r="I85" s="24"/>
       <c r="J85" s="24"/>
       <c r="K85" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L85" s="26"/>
@@ -5098,7 +5260,7 @@
       </c>
       <c r="P85" s="22"/>
     </row>
-    <row r="86" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B86" s="20">
         <v>76</v>
       </c>
@@ -5114,7 +5276,7 @@
       <c r="I86" s="24"/>
       <c r="J86" s="24"/>
       <c r="K86" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L86" s="26"/>
@@ -5129,7 +5291,7 @@
       </c>
       <c r="P86" s="22"/>
     </row>
-    <row r="87" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B87" s="20">
         <v>77</v>
       </c>
@@ -5145,7 +5307,7 @@
       <c r="I87" s="24"/>
       <c r="J87" s="24"/>
       <c r="K87" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L87" s="26"/>
@@ -5160,7 +5322,7 @@
       </c>
       <c r="P87" s="22"/>
     </row>
-    <row r="88" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B88" s="20">
         <v>78</v>
       </c>
@@ -5176,7 +5338,7 @@
       <c r="I88" s="24"/>
       <c r="J88" s="24"/>
       <c r="K88" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L88" s="26"/>
@@ -5191,7 +5353,7 @@
       </c>
       <c r="P88" s="22"/>
     </row>
-    <row r="89" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B89" s="20">
         <v>79</v>
       </c>
@@ -5207,7 +5369,7 @@
       <c r="I89" s="24"/>
       <c r="J89" s="24"/>
       <c r="K89" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L89" s="26"/>
@@ -5222,7 +5384,7 @@
       </c>
       <c r="P89" s="22"/>
     </row>
-    <row r="90" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B90" s="20">
         <v>80</v>
       </c>
@@ -5238,7 +5400,7 @@
       <c r="I90" s="24"/>
       <c r="J90" s="24"/>
       <c r="K90" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L90" s="26"/>
@@ -5253,7 +5415,7 @@
       </c>
       <c r="P90" s="22"/>
     </row>
-    <row r="91" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B91" s="20">
         <v>81</v>
       </c>
@@ -5269,7 +5431,7 @@
       <c r="I91" s="24"/>
       <c r="J91" s="24"/>
       <c r="K91" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L91" s="26"/>
@@ -5284,7 +5446,7 @@
       </c>
       <c r="P91" s="22"/>
     </row>
-    <row r="92" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B92" s="20">
         <v>82</v>
       </c>
@@ -5300,7 +5462,7 @@
       <c r="I92" s="24"/>
       <c r="J92" s="24"/>
       <c r="K92" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L92" s="26"/>
@@ -5315,7 +5477,7 @@
       </c>
       <c r="P92" s="22"/>
     </row>
-    <row r="93" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B93" s="20">
         <v>83</v>
       </c>
@@ -5331,7 +5493,7 @@
       <c r="I93" s="24"/>
       <c r="J93" s="24"/>
       <c r="K93" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L93" s="26"/>
@@ -5346,7 +5508,7 @@
       </c>
       <c r="P93" s="22"/>
     </row>
-    <row r="94" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B94" s="20">
         <v>84</v>
       </c>
@@ -5362,7 +5524,7 @@
       <c r="I94" s="24"/>
       <c r="J94" s="24"/>
       <c r="K94" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L94" s="26"/>
@@ -5377,7 +5539,7 @@
       </c>
       <c r="P94" s="22"/>
     </row>
-    <row r="95" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B95" s="20">
         <v>85</v>
       </c>
@@ -5393,7 +5555,7 @@
       <c r="I95" s="24"/>
       <c r="J95" s="24"/>
       <c r="K95" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L95" s="26"/>
@@ -5408,7 +5570,7 @@
       </c>
       <c r="P95" s="22"/>
     </row>
-    <row r="96" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B96" s="20">
         <v>86</v>
       </c>
@@ -5424,7 +5586,7 @@
       <c r="I96" s="24"/>
       <c r="J96" s="24"/>
       <c r="K96" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L96" s="26"/>
@@ -5439,7 +5601,7 @@
       </c>
       <c r="P96" s="22"/>
     </row>
-    <row r="97" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B97" s="20">
         <v>87</v>
       </c>
@@ -5455,7 +5617,7 @@
       <c r="I97" s="24"/>
       <c r="J97" s="24"/>
       <c r="K97" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L97" s="26"/>
@@ -5470,7 +5632,7 @@
       </c>
       <c r="P97" s="22"/>
     </row>
-    <row r="98" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B98" s="20">
         <v>88</v>
       </c>
@@ -5486,7 +5648,7 @@
       <c r="I98" s="24"/>
       <c r="J98" s="24"/>
       <c r="K98" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L98" s="26"/>
@@ -5501,7 +5663,7 @@
       </c>
       <c r="P98" s="22"/>
     </row>
-    <row r="99" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B99" s="20">
         <v>89</v>
       </c>
@@ -5517,7 +5679,7 @@
       <c r="I99" s="24"/>
       <c r="J99" s="24"/>
       <c r="K99" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L99" s="26"/>
@@ -5532,7 +5694,7 @@
       </c>
       <c r="P99" s="22"/>
     </row>
-    <row r="100" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B100" s="20">
         <v>90</v>
       </c>
@@ -5548,7 +5710,7 @@
       <c r="I100" s="24"/>
       <c r="J100" s="24"/>
       <c r="K100" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L100" s="26"/>
@@ -5563,7 +5725,7 @@
       </c>
       <c r="P100" s="22"/>
     </row>
-    <row r="101" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B101" s="20">
         <v>91</v>
       </c>
@@ -5579,7 +5741,7 @@
       <c r="I101" s="24"/>
       <c r="J101" s="24"/>
       <c r="K101" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L101" s="26"/>
@@ -5594,7 +5756,7 @@
       </c>
       <c r="P101" s="22"/>
     </row>
-    <row r="102" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B102" s="20">
         <v>92</v>
       </c>
@@ -5610,7 +5772,7 @@
       <c r="I102" s="24"/>
       <c r="J102" s="24"/>
       <c r="K102" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L102" s="26"/>
@@ -5625,7 +5787,7 @@
       </c>
       <c r="P102" s="22"/>
     </row>
-    <row r="103" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B103" s="20">
         <v>93</v>
       </c>
@@ -5641,7 +5803,7 @@
       <c r="I103" s="24"/>
       <c r="J103" s="24"/>
       <c r="K103" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L103" s="26"/>
@@ -5656,7 +5818,7 @@
       </c>
       <c r="P103" s="22"/>
     </row>
-    <row r="104" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B104" s="20">
         <v>94</v>
       </c>
@@ -5672,7 +5834,7 @@
       <c r="I104" s="24"/>
       <c r="J104" s="24"/>
       <c r="K104" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L104" s="26"/>
@@ -5687,7 +5849,7 @@
       </c>
       <c r="P104" s="22"/>
     </row>
-    <row r="105" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B105" s="20">
         <v>95</v>
       </c>
@@ -5703,7 +5865,7 @@
       <c r="I105" s="24"/>
       <c r="J105" s="24"/>
       <c r="K105" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L105" s="26"/>
@@ -5718,7 +5880,7 @@
       </c>
       <c r="P105" s="22"/>
     </row>
-    <row r="106" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B106" s="20">
         <v>96</v>
       </c>
@@ -5734,7 +5896,7 @@
       <c r="I106" s="24"/>
       <c r="J106" s="24"/>
       <c r="K106" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L106" s="26"/>
@@ -5749,7 +5911,7 @@
       </c>
       <c r="P106" s="22"/>
     </row>
-    <row r="107" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B107" s="20">
         <v>97</v>
       </c>
@@ -5765,7 +5927,7 @@
       <c r="I107" s="24"/>
       <c r="J107" s="24"/>
       <c r="K107" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L107" s="26"/>
@@ -5780,7 +5942,7 @@
       </c>
       <c r="P107" s="22"/>
     </row>
-    <row r="108" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B108" s="20">
         <v>98</v>
       </c>
@@ -5796,7 +5958,7 @@
       <c r="I108" s="24"/>
       <c r="J108" s="24"/>
       <c r="K108" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L108" s="26"/>
@@ -5811,7 +5973,7 @@
       </c>
       <c r="P108" s="22"/>
     </row>
-    <row r="109" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B109" s="20">
         <v>99</v>
       </c>
@@ -5827,7 +5989,7 @@
       <c r="I109" s="24"/>
       <c r="J109" s="24"/>
       <c r="K109" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L109" s="26"/>
@@ -5842,7 +6004,7 @@
       </c>
       <c r="P109" s="22"/>
     </row>
-    <row r="110" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B110" s="20">
         <v>100</v>
       </c>
@@ -5858,7 +6020,7 @@
       <c r="I110" s="24"/>
       <c r="J110" s="24"/>
       <c r="K110" s="25" t="str">
-        <f t="shared" ca="1" si="3"/>
+        <f t="shared" ca="1" si="5"/>
         <v/>
       </c>
       <c r="L110" s="26"/>
@@ -5882,24 +6044,20 @@
     <mergeCell ref="L9:M9"/>
     <mergeCell ref="N9:O9"/>
   </mergeCells>
-  <conditionalFormatting sqref="H11:H34 H44:H110">
-    <cfRule type="expression" dxfId="7" priority="4">
+  <phoneticPr fontId="7" type="noConversion"/>
+  <conditionalFormatting sqref="H11:H34 H52:H110">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>AND(H11&lt;&gt;"",COUNTIF($C$11:$C$110,H11)=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J11:J26 J29:J33 J44:J110">
-    <cfRule type="expression" dxfId="6" priority="5">
-      <formula>AND(I11&lt;&gt;"",J11&lt;&gt;"", I11&gt;J11)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H35:H43">
+  <conditionalFormatting sqref="H35:H51">
     <cfRule type="expression" dxfId="5" priority="1">
       <formula>AND(H35&lt;&gt;"",COUNTIF($C$11:$C$110,H35)=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J35:J43">
-    <cfRule type="expression" dxfId="4" priority="2">
-      <formula>AND(I35&lt;&gt;"",J35&lt;&gt;"", I35&gt;J35)</formula>
+  <conditionalFormatting sqref="J11:J26 J29:J33 J35:J110">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>AND(I11&lt;&gt;"",J11&lt;&gt;"", I11&gt;J11)</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="10">
@@ -5956,7 +6114,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>D11:D34 D44:D110</xm:sqref>
+          <xm:sqref>D11:D34 D52:D110 D44</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Assignee" prompt="Select the workmate the task is assigned to." xr:uid="{00000000-0002-0000-0200-000004000000}">
           <x14:formula1>
@@ -5965,7 +6123,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>E11:E34 E44:E110</xm:sqref>
+          <xm:sqref>E11:E34 E52:E110</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" operator="equal" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Role" prompt="Select a role from the select box.  Use &quot;other&quot; only in truly exceptional cases.  Consult your lecturer in such cases." xr:uid="{00000000-0002-0000-0200-000005000000}">
           <x14:formula1>
@@ -5974,7 +6132,7 @@
           <x14:formula2>
             <xm:f>0</xm:f>
           </x14:formula2>
-          <xm:sqref>F11:F34 F44:F110</xm:sqref>
+          <xm:sqref>F11:F34 F52:F110</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5985,49 +6143,49 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:P110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="15" width="18.85546875" customWidth="1"/>
-    <col min="16" max="16" width="64.5703125" customWidth="1"/>
+    <col min="3" max="15" width="18.88671875" customWidth="1"/>
+    <col min="16" max="16" width="64.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="C2" s="54" t="s">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C2" s="63" t="s">
         <v>71</v>
       </c>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="54"/>
-    </row>
-    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="55" t="s">
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+    </row>
+    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="55"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="55"/>
-      <c r="O4" s="55"/>
-      <c r="P4" s="55"/>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="64"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -6043,8 +6201,8 @@
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
     </row>
-    <row r="6" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="56" t="s">
+    <row r="6" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="65" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -6052,7 +6210,7 @@
       </c>
       <c r="E6" s="11">
         <f>SUM(N11:N110)</f>
-        <v>875</v>
+        <v>1335</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
@@ -6066,18 +6224,18 @@
       <c r="O6" s="9"/>
       <c r="P6" s="9"/>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="C7" s="56"/>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C7" s="65"/>
       <c r="D7" s="12" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="13">
         <f>SUM(O11:O110)</f>
-        <v>955</v>
+        <v>1275</v>
       </c>
       <c r="J7" s="14"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" s="15"/>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
@@ -6085,22 +6243,22 @@
       <c r="F9" s="16"/>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
-      <c r="I9" s="57" t="s">
+      <c r="I9" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="57"/>
+      <c r="J9" s="66"/>
       <c r="K9" s="16"/>
-      <c r="L9" s="57" t="s">
+      <c r="L9" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="M9" s="57"/>
-      <c r="N9" s="57" t="s">
+      <c r="M9" s="66"/>
+      <c r="N9" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="O9" s="57"/>
+      <c r="O9" s="66"/>
       <c r="P9" s="16"/>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" s="17" t="s">
         <v>17</v>
       </c>
@@ -6147,7 +6305,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B11" s="20">
         <v>1</v>
       </c>
@@ -6196,7 +6354,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B12" s="20">
         <v>2</v>
       </c>
@@ -6245,7 +6403,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B13" s="20">
         <v>3</v>
       </c>
@@ -6296,7 +6454,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B14" s="20">
         <v>4</v>
       </c>
@@ -6347,7 +6505,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B15" s="20">
         <v>5</v>
       </c>
@@ -6398,7 +6556,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B16" s="20">
         <v>6</v>
       </c>
@@ -6449,7 +6607,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B17" s="20">
         <v>7</v>
       </c>
@@ -6498,7 +6656,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B18" s="20">
         <v>8</v>
       </c>
@@ -6547,7 +6705,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B19" s="20">
         <v>9</v>
       </c>
@@ -6596,7 +6754,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B20" s="20">
         <v>10</v>
       </c>
@@ -6645,7 +6803,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B21" s="20">
         <v>11</v>
       </c>
@@ -6694,7 +6852,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B22" s="20">
         <v>12</v>
       </c>
@@ -6743,7 +6901,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B23" s="20">
         <v>13</v>
       </c>
@@ -6792,69 +6950,105 @@
         <v>126</v>
       </c>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B24" s="20">
         <v>14</v>
       </c>
       <c r="C24" s="21" t="str">
         <f>IF(ISBLANK(D24), "", _xlfn.CONCAT("T", TEXT(B24, "0000"), "/", VLOOKUP(D24, Internal!$B$35:C$39, 2, FALSE()), IF(OR(D24="QA", D24="Revision"), _xlfn.CONCAT("/", H24), "")))</f>
-        <v/>
-      </c>
-      <c r="D24" s="22"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="22"/>
+        <v>T0014/D</v>
+      </c>
+      <c r="D24" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="F24" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="G24" s="22" t="s">
+        <v>63</v>
+      </c>
       <c r="H24" s="23"/>
-      <c r="I24" s="24"/>
-      <c r="J24" s="24"/>
+      <c r="I24" s="24">
+        <v>46114.416666666664</v>
+      </c>
+      <c r="J24" s="24">
+        <v>46114.833333333336</v>
+      </c>
       <c r="K24" s="25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L24" s="26"/>
-      <c r="M24" s="26"/>
-      <c r="N24" s="25" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L24" s="26">
+        <v>10</v>
+      </c>
+      <c r="M24" s="26">
+        <v>8</v>
+      </c>
+      <c r="N24" s="25">
         <f>IF(ISBLANK(L24), "", L24*VLOOKUP($F24,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="O24" s="25" t="str">
+        <v>300</v>
+      </c>
+      <c r="O24" s="25">
         <f>IF(ISBLANK(M24), "", M24*VLOOKUP($F24,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="P24" s="22"/>
-    </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
+        <v>240</v>
+      </c>
+      <c r="P24" s="22" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B25" s="20">
         <v>15</v>
       </c>
       <c r="C25" s="21" t="str">
         <f>IF(ISBLANK(D25), "", _xlfn.CONCAT("T", TEXT(B25, "0000"), "/", VLOOKUP(D25, Internal!$B$35:C$39, 2, FALSE()), IF(OR(D25="QA", D25="Revision"), _xlfn.CONCAT("/", H25), "")))</f>
-        <v/>
-      </c>
-      <c r="D25" s="22"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="22"/>
+        <v>T0015/D</v>
+      </c>
+      <c r="D25" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="F25" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="G25" s="22" t="s">
+        <v>46</v>
+      </c>
       <c r="H25" s="23"/>
-      <c r="I25" s="24"/>
-      <c r="J25" s="24"/>
+      <c r="I25" s="24">
+        <v>46120.75</v>
+      </c>
+      <c r="J25" s="24">
+        <v>46120.833333333336</v>
+      </c>
       <c r="K25" s="25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L25" s="26"/>
-      <c r="M25" s="26"/>
-      <c r="N25" s="25" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L25" s="26">
+        <v>4</v>
+      </c>
+      <c r="M25" s="26">
+        <v>2</v>
+      </c>
+      <c r="N25" s="25">
         <f>IF(ISBLANK(L25), "", L25*VLOOKUP($F25,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="O25" s="25" t="str">
+        <v>160</v>
+      </c>
+      <c r="O25" s="25">
         <f>IF(ISBLANK(M25), "", M25*VLOOKUP($F25,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="P25" s="22"/>
-    </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="P25" s="22" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B26" s="20">
         <v>16</v>
       </c>
@@ -6885,7 +7079,7 @@
       </c>
       <c r="P26" s="22"/>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B27" s="20">
         <v>17</v>
       </c>
@@ -6916,7 +7110,7 @@
       </c>
       <c r="P27" s="22"/>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B28" s="20">
         <v>18</v>
       </c>
@@ -6947,7 +7141,7 @@
       </c>
       <c r="P28" s="22"/>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B29" s="20">
         <v>19</v>
       </c>
@@ -6978,7 +7172,7 @@
       </c>
       <c r="P29" s="22"/>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B30" s="20">
         <v>20</v>
       </c>
@@ -7009,7 +7203,7 @@
       </c>
       <c r="P30" s="22"/>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B31" s="20">
         <v>21</v>
       </c>
@@ -7040,7 +7234,7 @@
       </c>
       <c r="P31" s="22"/>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B32" s="20">
         <v>22</v>
       </c>
@@ -7071,7 +7265,7 @@
       </c>
       <c r="P32" s="22"/>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B33" s="20">
         <v>23</v>
       </c>
@@ -7102,7 +7296,7 @@
       </c>
       <c r="P33" s="22"/>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B34" s="20">
         <v>24</v>
       </c>
@@ -7133,7 +7327,7 @@
       </c>
       <c r="P34" s="22"/>
     </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B35" s="20">
         <v>25</v>
       </c>
@@ -7164,7 +7358,7 @@
       </c>
       <c r="P35" s="22"/>
     </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B36" s="20">
         <v>26</v>
       </c>
@@ -7195,7 +7389,7 @@
       </c>
       <c r="P36" s="22"/>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B37" s="20">
         <v>27</v>
       </c>
@@ -7226,7 +7420,7 @@
       </c>
       <c r="P37" s="22"/>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B38" s="20">
         <v>28</v>
       </c>
@@ -7257,7 +7451,7 @@
       </c>
       <c r="P38" s="22"/>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B39" s="20">
         <v>29</v>
       </c>
@@ -7288,7 +7482,7 @@
       </c>
       <c r="P39" s="22"/>
     </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B40" s="20">
         <v>30</v>
       </c>
@@ -7319,7 +7513,7 @@
       </c>
       <c r="P40" s="22"/>
     </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B41" s="20">
         <v>31</v>
       </c>
@@ -7350,7 +7544,7 @@
       </c>
       <c r="P41" s="22"/>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B42" s="20">
         <v>32</v>
       </c>
@@ -7381,7 +7575,7 @@
       </c>
       <c r="P42" s="22"/>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B43" s="20">
         <v>33</v>
       </c>
@@ -7412,7 +7606,7 @@
       </c>
       <c r="P43" s="22"/>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B44" s="20">
         <v>34</v>
       </c>
@@ -7443,7 +7637,7 @@
       </c>
       <c r="P44" s="22"/>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B45" s="20">
         <v>35</v>
       </c>
@@ -7474,7 +7668,7 @@
       </c>
       <c r="P45" s="22"/>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B46" s="20">
         <v>36</v>
       </c>
@@ -7505,7 +7699,7 @@
       </c>
       <c r="P46" s="22"/>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B47" s="20">
         <v>37</v>
       </c>
@@ -7536,7 +7730,7 @@
       </c>
       <c r="P47" s="22"/>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B48" s="20">
         <v>38</v>
       </c>
@@ -7567,7 +7761,7 @@
       </c>
       <c r="P48" s="22"/>
     </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B49" s="20">
         <v>39</v>
       </c>
@@ -7598,7 +7792,7 @@
       </c>
       <c r="P49" s="22"/>
     </row>
-    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B50" s="20">
         <v>40</v>
       </c>
@@ -7629,7 +7823,7 @@
       </c>
       <c r="P50" s="22"/>
     </row>
-    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B51" s="20">
         <v>41</v>
       </c>
@@ -7660,7 +7854,7 @@
       </c>
       <c r="P51" s="22"/>
     </row>
-    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B52" s="20">
         <v>42</v>
       </c>
@@ -7691,7 +7885,7 @@
       </c>
       <c r="P52" s="22"/>
     </row>
-    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B53" s="20">
         <v>43</v>
       </c>
@@ -7722,7 +7916,7 @@
       </c>
       <c r="P53" s="22"/>
     </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B54" s="20">
         <v>44</v>
       </c>
@@ -7753,7 +7947,7 @@
       </c>
       <c r="P54" s="22"/>
     </row>
-    <row r="55" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B55" s="20">
         <v>45</v>
       </c>
@@ -7784,7 +7978,7 @@
       </c>
       <c r="P55" s="22"/>
     </row>
-    <row r="56" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B56" s="20">
         <v>46</v>
       </c>
@@ -7815,7 +8009,7 @@
       </c>
       <c r="P56" s="22"/>
     </row>
-    <row r="57" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B57" s="20">
         <v>47</v>
       </c>
@@ -7846,7 +8040,7 @@
       </c>
       <c r="P57" s="22"/>
     </row>
-    <row r="58" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B58" s="20">
         <v>48</v>
       </c>
@@ -7877,7 +8071,7 @@
       </c>
       <c r="P58" s="22"/>
     </row>
-    <row r="59" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B59" s="20">
         <v>49</v>
       </c>
@@ -7908,7 +8102,7 @@
       </c>
       <c r="P59" s="22"/>
     </row>
-    <row r="60" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B60" s="20">
         <v>50</v>
       </c>
@@ -7939,7 +8133,7 @@
       </c>
       <c r="P60" s="22"/>
     </row>
-    <row r="61" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B61" s="20">
         <v>51</v>
       </c>
@@ -7970,7 +8164,7 @@
       </c>
       <c r="P61" s="22"/>
     </row>
-    <row r="62" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B62" s="20">
         <v>52</v>
       </c>
@@ -8001,7 +8195,7 @@
       </c>
       <c r="P62" s="22"/>
     </row>
-    <row r="63" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B63" s="20">
         <v>53</v>
       </c>
@@ -8032,7 +8226,7 @@
       </c>
       <c r="P63" s="22"/>
     </row>
-    <row r="64" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B64" s="20">
         <v>54</v>
       </c>
@@ -8063,7 +8257,7 @@
       </c>
       <c r="P64" s="22"/>
     </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B65" s="20">
         <v>55</v>
       </c>
@@ -8094,7 +8288,7 @@
       </c>
       <c r="P65" s="22"/>
     </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B66" s="20">
         <v>56</v>
       </c>
@@ -8125,7 +8319,7 @@
       </c>
       <c r="P66" s="22"/>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B67" s="20">
         <v>57</v>
       </c>
@@ -8156,7 +8350,7 @@
       </c>
       <c r="P67" s="22"/>
     </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B68" s="20">
         <v>58</v>
       </c>
@@ -8187,7 +8381,7 @@
       </c>
       <c r="P68" s="22"/>
     </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B69" s="20">
         <v>59</v>
       </c>
@@ -8218,7 +8412,7 @@
       </c>
       <c r="P69" s="22"/>
     </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B70" s="20">
         <v>60</v>
       </c>
@@ -8249,7 +8443,7 @@
       </c>
       <c r="P70" s="22"/>
     </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B71" s="20">
         <v>61</v>
       </c>
@@ -8280,7 +8474,7 @@
       </c>
       <c r="P71" s="22"/>
     </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B72" s="20">
         <v>62</v>
       </c>
@@ -8311,7 +8505,7 @@
       </c>
       <c r="P72" s="22"/>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B73" s="20">
         <v>63</v>
       </c>
@@ -8342,7 +8536,7 @@
       </c>
       <c r="P73" s="22"/>
     </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B74" s="20">
         <v>64</v>
       </c>
@@ -8373,7 +8567,7 @@
       </c>
       <c r="P74" s="22"/>
     </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B75" s="20">
         <v>65</v>
       </c>
@@ -8404,7 +8598,7 @@
       </c>
       <c r="P75" s="22"/>
     </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B76" s="20">
         <v>66</v>
       </c>
@@ -8435,7 +8629,7 @@
       </c>
       <c r="P76" s="22"/>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B77" s="20">
         <v>67</v>
       </c>
@@ -8466,7 +8660,7 @@
       </c>
       <c r="P77" s="22"/>
     </row>
-    <row r="78" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B78" s="20">
         <v>68</v>
       </c>
@@ -8497,7 +8691,7 @@
       </c>
       <c r="P78" s="22"/>
     </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B79" s="20">
         <v>69</v>
       </c>
@@ -8528,7 +8722,7 @@
       </c>
       <c r="P79" s="22"/>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B80" s="20">
         <v>70</v>
       </c>
@@ -8559,7 +8753,7 @@
       </c>
       <c r="P80" s="22"/>
     </row>
-    <row r="81" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B81" s="20">
         <v>71</v>
       </c>
@@ -8590,7 +8784,7 @@
       </c>
       <c r="P81" s="22"/>
     </row>
-    <row r="82" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B82" s="20">
         <v>72</v>
       </c>
@@ -8621,7 +8815,7 @@
       </c>
       <c r="P82" s="22"/>
     </row>
-    <row r="83" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B83" s="20">
         <v>73</v>
       </c>
@@ -8652,7 +8846,7 @@
       </c>
       <c r="P83" s="22"/>
     </row>
-    <row r="84" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B84" s="20">
         <v>74</v>
       </c>
@@ -8683,7 +8877,7 @@
       </c>
       <c r="P84" s="22"/>
     </row>
-    <row r="85" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B85" s="20">
         <v>75</v>
       </c>
@@ -8714,7 +8908,7 @@
       </c>
       <c r="P85" s="22"/>
     </row>
-    <row r="86" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B86" s="20">
         <v>76</v>
       </c>
@@ -8745,7 +8939,7 @@
       </c>
       <c r="P86" s="22"/>
     </row>
-    <row r="87" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B87" s="20">
         <v>77</v>
       </c>
@@ -8776,7 +8970,7 @@
       </c>
       <c r="P87" s="22"/>
     </row>
-    <row r="88" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B88" s="20">
         <v>78</v>
       </c>
@@ -8807,7 +9001,7 @@
       </c>
       <c r="P88" s="22"/>
     </row>
-    <row r="89" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B89" s="20">
         <v>79</v>
       </c>
@@ -8838,7 +9032,7 @@
       </c>
       <c r="P89" s="22"/>
     </row>
-    <row r="90" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B90" s="20">
         <v>80</v>
       </c>
@@ -8869,7 +9063,7 @@
       </c>
       <c r="P90" s="22"/>
     </row>
-    <row r="91" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B91" s="20">
         <v>81</v>
       </c>
@@ -8900,7 +9094,7 @@
       </c>
       <c r="P91" s="22"/>
     </row>
-    <row r="92" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B92" s="20">
         <v>82</v>
       </c>
@@ -8931,7 +9125,7 @@
       </c>
       <c r="P92" s="22"/>
     </row>
-    <row r="93" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B93" s="20">
         <v>83</v>
       </c>
@@ -8962,7 +9156,7 @@
       </c>
       <c r="P93" s="22"/>
     </row>
-    <row r="94" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B94" s="20">
         <v>84</v>
       </c>
@@ -8993,7 +9187,7 @@
       </c>
       <c r="P94" s="22"/>
     </row>
-    <row r="95" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B95" s="20">
         <v>85</v>
       </c>
@@ -9024,7 +9218,7 @@
       </c>
       <c r="P95" s="22"/>
     </row>
-    <row r="96" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B96" s="20">
         <v>86</v>
       </c>
@@ -9055,7 +9249,7 @@
       </c>
       <c r="P96" s="22"/>
     </row>
-    <row r="97" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B97" s="20">
         <v>87</v>
       </c>
@@ -9086,7 +9280,7 @@
       </c>
       <c r="P97" s="22"/>
     </row>
-    <row r="98" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B98" s="20">
         <v>88</v>
       </c>
@@ -9117,7 +9311,7 @@
       </c>
       <c r="P98" s="22"/>
     </row>
-    <row r="99" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B99" s="20">
         <v>89</v>
       </c>
@@ -9148,7 +9342,7 @@
       </c>
       <c r="P99" s="22"/>
     </row>
-    <row r="100" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B100" s="20">
         <v>90</v>
       </c>
@@ -9179,7 +9373,7 @@
       </c>
       <c r="P100" s="22"/>
     </row>
-    <row r="101" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B101" s="20">
         <v>91</v>
       </c>
@@ -9210,7 +9404,7 @@
       </c>
       <c r="P101" s="22"/>
     </row>
-    <row r="102" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B102" s="20">
         <v>92</v>
       </c>
@@ -9241,7 +9435,7 @@
       </c>
       <c r="P102" s="22"/>
     </row>
-    <row r="103" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B103" s="20">
         <v>93</v>
       </c>
@@ -9272,7 +9466,7 @@
       </c>
       <c r="P103" s="22"/>
     </row>
-    <row r="104" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B104" s="20">
         <v>94</v>
       </c>
@@ -9303,7 +9497,7 @@
       </c>
       <c r="P104" s="22"/>
     </row>
-    <row r="105" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B105" s="20">
         <v>95</v>
       </c>
@@ -9334,7 +9528,7 @@
       </c>
       <c r="P105" s="22"/>
     </row>
-    <row r="106" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B106" s="20">
         <v>96</v>
       </c>
@@ -9365,7 +9559,7 @@
       </c>
       <c r="P106" s="22"/>
     </row>
-    <row r="107" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B107" s="20">
         <v>97</v>
       </c>
@@ -9396,7 +9590,7 @@
       </c>
       <c r="P107" s="22"/>
     </row>
-    <row r="108" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B108" s="20">
         <v>98</v>
       </c>
@@ -9427,7 +9621,7 @@
       </c>
       <c r="P108" s="22"/>
     </row>
-    <row r="109" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B109" s="20">
         <v>99</v>
       </c>
@@ -9458,7 +9652,7 @@
       </c>
       <c r="P109" s="22"/>
     </row>
-    <row r="110" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B110" s="20">
         <v>100</v>
       </c>
@@ -9503,7 +9697,7 @@
       <formula>AND(H11&lt;&gt;"",COUNTIF($C$11:$C$110,H11)=0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J11:J16 J24:J110">
+  <conditionalFormatting sqref="J11:J16 J26:J110">
     <cfRule type="expression" dxfId="2" priority="3">
       <formula>AND(I11&lt;&gt;"",J11&lt;&gt;"", I11&gt;J11)</formula>
     </cfRule>
@@ -9596,49 +9790,49 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B2:P110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="15" width="18.85546875" customWidth="1"/>
-    <col min="16" max="16" width="64.5703125" customWidth="1"/>
+    <col min="3" max="15" width="18.88671875" customWidth="1"/>
+    <col min="16" max="16" width="64.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="C2" s="54" t="s">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C2" s="63" t="s">
         <v>87</v>
       </c>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="M2" s="54"/>
-      <c r="N2" s="54"/>
-      <c r="O2" s="54"/>
-      <c r="P2" s="54"/>
-    </row>
-    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C4" s="55" t="s">
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+      <c r="K2" s="63"/>
+      <c r="L2" s="63"/>
+      <c r="M2" s="63"/>
+      <c r="N2" s="63"/>
+      <c r="O2" s="63"/>
+      <c r="P2" s="63"/>
+    </row>
+    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="64" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-      <c r="K4" s="55"/>
-      <c r="L4" s="55"/>
-      <c r="M4" s="55"/>
-      <c r="N4" s="55"/>
-      <c r="O4" s="55"/>
-      <c r="P4" s="55"/>
-    </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.25">
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+      <c r="K4" s="64"/>
+      <c r="L4" s="64"/>
+      <c r="M4" s="64"/>
+      <c r="N4" s="64"/>
+      <c r="O4" s="64"/>
+      <c r="P4" s="64"/>
+    </row>
+    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -9654,8 +9848,8 @@
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
     </row>
-    <row r="6" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="C6" s="56" t="s">
+    <row r="6" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="65" t="s">
         <v>11</v>
       </c>
       <c r="D6" s="10" t="s">
@@ -9677,8 +9871,8 @@
       <c r="O6" s="9"/>
       <c r="P6" s="9"/>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="C7" s="56"/>
+    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
+      <c r="C7" s="65"/>
       <c r="D7" s="12" t="s">
         <v>13</v>
       </c>
@@ -9688,7 +9882,7 @@
       </c>
       <c r="J7" s="14"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B9" s="15"/>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
@@ -9696,22 +9890,22 @@
       <c r="F9" s="16"/>
       <c r="G9" s="16"/>
       <c r="H9" s="16"/>
-      <c r="I9" s="57" t="s">
+      <c r="I9" s="66" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="57"/>
+      <c r="J9" s="66"/>
       <c r="K9" s="16"/>
-      <c r="L9" s="57" t="s">
+      <c r="L9" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="M9" s="57"/>
-      <c r="N9" s="57" t="s">
+      <c r="M9" s="66"/>
+      <c r="N9" s="66" t="s">
         <v>16</v>
       </c>
-      <c r="O9" s="57"/>
+      <c r="O9" s="66"/>
       <c r="P9" s="16"/>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B10" s="17" t="s">
         <v>17</v>
       </c>
@@ -9758,7 +9952,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B11" s="20">
         <v>1</v>
       </c>
@@ -9789,7 +9983,7 @@
       </c>
       <c r="P11" s="22"/>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B12" s="20">
         <v>2</v>
       </c>
@@ -9820,7 +10014,7 @@
       </c>
       <c r="P12" s="22"/>
     </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B13" s="20">
         <v>3</v>
       </c>
@@ -9851,7 +10045,7 @@
       </c>
       <c r="P13" s="22"/>
     </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B14" s="20">
         <v>4</v>
       </c>
@@ -9882,7 +10076,7 @@
       </c>
       <c r="P14" s="22"/>
     </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B15" s="20">
         <v>5</v>
       </c>
@@ -9913,7 +10107,7 @@
       </c>
       <c r="P15" s="22"/>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B16" s="20">
         <v>6</v>
       </c>
@@ -9944,7 +10138,7 @@
       </c>
       <c r="P16" s="22"/>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B17" s="20">
         <v>7</v>
       </c>
@@ -9975,7 +10169,7 @@
       </c>
       <c r="P17" s="22"/>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B18" s="20">
         <v>8</v>
       </c>
@@ -10006,7 +10200,7 @@
       </c>
       <c r="P18" s="22"/>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B19" s="20">
         <v>9</v>
       </c>
@@ -10037,7 +10231,7 @@
       </c>
       <c r="P19" s="22"/>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B20" s="20">
         <v>10</v>
       </c>
@@ -10068,7 +10262,7 @@
       </c>
       <c r="P20" s="22"/>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B21" s="20">
         <v>11</v>
       </c>
@@ -10099,7 +10293,7 @@
       </c>
       <c r="P21" s="22"/>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B22" s="20">
         <v>12</v>
       </c>
@@ -10130,7 +10324,7 @@
       </c>
       <c r="P22" s="22"/>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B23" s="20">
         <v>13</v>
       </c>
@@ -10161,7 +10355,7 @@
       </c>
       <c r="P23" s="22"/>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B24" s="20">
         <v>14</v>
       </c>
@@ -10192,7 +10386,7 @@
       </c>
       <c r="P24" s="22"/>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B25" s="20">
         <v>15</v>
       </c>
@@ -10223,7 +10417,7 @@
       </c>
       <c r="P25" s="22"/>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B26" s="20">
         <v>16</v>
       </c>
@@ -10254,7 +10448,7 @@
       </c>
       <c r="P26" s="22"/>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B27" s="20">
         <v>17</v>
       </c>
@@ -10285,7 +10479,7 @@
       </c>
       <c r="P27" s="22"/>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B28" s="20">
         <v>18</v>
       </c>
@@ -10316,7 +10510,7 @@
       </c>
       <c r="P28" s="22"/>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B29" s="20">
         <v>19</v>
       </c>
@@ -10347,7 +10541,7 @@
       </c>
       <c r="P29" s="22"/>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B30" s="20">
         <v>20</v>
       </c>
@@ -10378,7 +10572,7 @@
       </c>
       <c r="P30" s="22"/>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B31" s="20">
         <v>21</v>
       </c>
@@ -10409,7 +10603,7 @@
       </c>
       <c r="P31" s="22"/>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B32" s="20">
         <v>22</v>
       </c>
@@ -10440,7 +10634,7 @@
       </c>
       <c r="P32" s="22"/>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B33" s="20">
         <v>23</v>
       </c>
@@ -10471,7 +10665,7 @@
       </c>
       <c r="P33" s="22"/>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B34" s="20">
         <v>24</v>
       </c>
@@ -10502,7 +10696,7 @@
       </c>
       <c r="P34" s="22"/>
     </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B35" s="20">
         <v>25</v>
       </c>
@@ -10533,7 +10727,7 @@
       </c>
       <c r="P35" s="22"/>
     </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B36" s="20">
         <v>26</v>
       </c>
@@ -10564,7 +10758,7 @@
       </c>
       <c r="P36" s="22"/>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B37" s="20">
         <v>27</v>
       </c>
@@ -10595,7 +10789,7 @@
       </c>
       <c r="P37" s="22"/>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B38" s="20">
         <v>28</v>
       </c>
@@ -10626,7 +10820,7 @@
       </c>
       <c r="P38" s="22"/>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B39" s="20">
         <v>29</v>
       </c>
@@ -10657,7 +10851,7 @@
       </c>
       <c r="P39" s="22"/>
     </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B40" s="20">
         <v>30</v>
       </c>
@@ -10688,7 +10882,7 @@
       </c>
       <c r="P40" s="22"/>
     </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B41" s="20">
         <v>31</v>
       </c>
@@ -10719,7 +10913,7 @@
       </c>
       <c r="P41" s="22"/>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B42" s="20">
         <v>32</v>
       </c>
@@ -10750,7 +10944,7 @@
       </c>
       <c r="P42" s="22"/>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B43" s="20">
         <v>33</v>
       </c>
@@ -10781,7 +10975,7 @@
       </c>
       <c r="P43" s="22"/>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B44" s="20">
         <v>34</v>
       </c>
@@ -10812,7 +11006,7 @@
       </c>
       <c r="P44" s="22"/>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B45" s="20">
         <v>35</v>
       </c>
@@ -10843,7 +11037,7 @@
       </c>
       <c r="P45" s="22"/>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B46" s="20">
         <v>36</v>
       </c>
@@ -10874,7 +11068,7 @@
       </c>
       <c r="P46" s="22"/>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B47" s="20">
         <v>37</v>
       </c>
@@ -10905,7 +11099,7 @@
       </c>
       <c r="P47" s="22"/>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B48" s="20">
         <v>38</v>
       </c>
@@ -10936,7 +11130,7 @@
       </c>
       <c r="P48" s="22"/>
     </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B49" s="20">
         <v>39</v>
       </c>
@@ -10967,7 +11161,7 @@
       </c>
       <c r="P49" s="22"/>
     </row>
-    <row r="50" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B50" s="20">
         <v>40</v>
       </c>
@@ -10998,7 +11192,7 @@
       </c>
       <c r="P50" s="22"/>
     </row>
-    <row r="51" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B51" s="20">
         <v>41</v>
       </c>
@@ -11029,7 +11223,7 @@
       </c>
       <c r="P51" s="22"/>
     </row>
-    <row r="52" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B52" s="20">
         <v>42</v>
       </c>
@@ -11060,7 +11254,7 @@
       </c>
       <c r="P52" s="22"/>
     </row>
-    <row r="53" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B53" s="20">
         <v>43</v>
       </c>
@@ -11091,7 +11285,7 @@
       </c>
       <c r="P53" s="22"/>
     </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B54" s="20">
         <v>44</v>
       </c>
@@ -11122,7 +11316,7 @@
       </c>
       <c r="P54" s="22"/>
     </row>
-    <row r="55" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B55" s="20">
         <v>45</v>
       </c>
@@ -11153,7 +11347,7 @@
       </c>
       <c r="P55" s="22"/>
     </row>
-    <row r="56" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B56" s="20">
         <v>46</v>
       </c>
@@ -11184,7 +11378,7 @@
       </c>
       <c r="P56" s="22"/>
     </row>
-    <row r="57" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B57" s="20">
         <v>47</v>
       </c>
@@ -11215,7 +11409,7 @@
       </c>
       <c r="P57" s="22"/>
     </row>
-    <row r="58" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B58" s="20">
         <v>48</v>
       </c>
@@ -11246,7 +11440,7 @@
       </c>
       <c r="P58" s="22"/>
     </row>
-    <row r="59" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B59" s="20">
         <v>49</v>
       </c>
@@ -11277,7 +11471,7 @@
       </c>
       <c r="P59" s="22"/>
     </row>
-    <row r="60" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B60" s="20">
         <v>50</v>
       </c>
@@ -11308,7 +11502,7 @@
       </c>
       <c r="P60" s="22"/>
     </row>
-    <row r="61" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B61" s="20">
         <v>51</v>
       </c>
@@ -11339,7 +11533,7 @@
       </c>
       <c r="P61" s="22"/>
     </row>
-    <row r="62" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B62" s="20">
         <v>52</v>
       </c>
@@ -11370,7 +11564,7 @@
       </c>
       <c r="P62" s="22"/>
     </row>
-    <row r="63" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B63" s="20">
         <v>53</v>
       </c>
@@ -11401,7 +11595,7 @@
       </c>
       <c r="P63" s="22"/>
     </row>
-    <row r="64" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B64" s="20">
         <v>54</v>
       </c>
@@ -11432,7 +11626,7 @@
       </c>
       <c r="P64" s="22"/>
     </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B65" s="20">
         <v>55</v>
       </c>
@@ -11463,7 +11657,7 @@
       </c>
       <c r="P65" s="22"/>
     </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B66" s="20">
         <v>56</v>
       </c>
@@ -11494,7 +11688,7 @@
       </c>
       <c r="P66" s="22"/>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B67" s="20">
         <v>57</v>
       </c>
@@ -11525,7 +11719,7 @@
       </c>
       <c r="P67" s="22"/>
     </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B68" s="20">
         <v>58</v>
       </c>
@@ -11556,7 +11750,7 @@
       </c>
       <c r="P68" s="22"/>
     </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B69" s="20">
         <v>59</v>
       </c>
@@ -11587,7 +11781,7 @@
       </c>
       <c r="P69" s="22"/>
     </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B70" s="20">
         <v>60</v>
       </c>
@@ -11618,7 +11812,7 @@
       </c>
       <c r="P70" s="22"/>
     </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B71" s="20">
         <v>61</v>
       </c>
@@ -11649,7 +11843,7 @@
       </c>
       <c r="P71" s="22"/>
     </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B72" s="20">
         <v>62</v>
       </c>
@@ -11680,7 +11874,7 @@
       </c>
       <c r="P72" s="22"/>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B73" s="20">
         <v>63</v>
       </c>
@@ -11711,7 +11905,7 @@
       </c>
       <c r="P73" s="22"/>
     </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B74" s="20">
         <v>64</v>
       </c>
@@ -11742,7 +11936,7 @@
       </c>
       <c r="P74" s="22"/>
     </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B75" s="20">
         <v>65</v>
       </c>
@@ -11773,7 +11967,7 @@
       </c>
       <c r="P75" s="22"/>
     </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B76" s="20">
         <v>66</v>
       </c>
@@ -11804,7 +11998,7 @@
       </c>
       <c r="P76" s="22"/>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B77" s="20">
         <v>67</v>
       </c>
@@ -11835,7 +12029,7 @@
       </c>
       <c r="P77" s="22"/>
     </row>
-    <row r="78" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B78" s="20">
         <v>68</v>
       </c>
@@ -11866,7 +12060,7 @@
       </c>
       <c r="P78" s="22"/>
     </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B79" s="20">
         <v>69</v>
       </c>
@@ -11897,7 +12091,7 @@
       </c>
       <c r="P79" s="22"/>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B80" s="20">
         <v>70</v>
       </c>
@@ -11928,7 +12122,7 @@
       </c>
       <c r="P80" s="22"/>
     </row>
-    <row r="81" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B81" s="20">
         <v>71</v>
       </c>
@@ -11959,7 +12153,7 @@
       </c>
       <c r="P81" s="22"/>
     </row>
-    <row r="82" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B82" s="20">
         <v>72</v>
       </c>
@@ -11990,7 +12184,7 @@
       </c>
       <c r="P82" s="22"/>
     </row>
-    <row r="83" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B83" s="20">
         <v>73</v>
       </c>
@@ -12021,7 +12215,7 @@
       </c>
       <c r="P83" s="22"/>
     </row>
-    <row r="84" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B84" s="20">
         <v>74</v>
       </c>
@@ -12052,7 +12246,7 @@
       </c>
       <c r="P84" s="22"/>
     </row>
-    <row r="85" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B85" s="20">
         <v>75</v>
       </c>
@@ -12083,7 +12277,7 @@
       </c>
       <c r="P85" s="22"/>
     </row>
-    <row r="86" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B86" s="20">
         <v>76</v>
       </c>
@@ -12114,7 +12308,7 @@
       </c>
       <c r="P86" s="22"/>
     </row>
-    <row r="87" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B87" s="20">
         <v>77</v>
       </c>
@@ -12145,7 +12339,7 @@
       </c>
       <c r="P87" s="22"/>
     </row>
-    <row r="88" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B88" s="20">
         <v>78</v>
       </c>
@@ -12176,7 +12370,7 @@
       </c>
       <c r="P88" s="22"/>
     </row>
-    <row r="89" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B89" s="20">
         <v>79</v>
       </c>
@@ -12207,7 +12401,7 @@
       </c>
       <c r="P89" s="22"/>
     </row>
-    <row r="90" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B90" s="20">
         <v>80</v>
       </c>
@@ -12238,7 +12432,7 @@
       </c>
       <c r="P90" s="22"/>
     </row>
-    <row r="91" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B91" s="20">
         <v>81</v>
       </c>
@@ -12269,7 +12463,7 @@
       </c>
       <c r="P91" s="22"/>
     </row>
-    <row r="92" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B92" s="20">
         <v>82</v>
       </c>
@@ -12300,7 +12494,7 @@
       </c>
       <c r="P92" s="22"/>
     </row>
-    <row r="93" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B93" s="20">
         <v>83</v>
       </c>
@@ -12331,7 +12525,7 @@
       </c>
       <c r="P93" s="22"/>
     </row>
-    <row r="94" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B94" s="20">
         <v>84</v>
       </c>
@@ -12362,7 +12556,7 @@
       </c>
       <c r="P94" s="22"/>
     </row>
-    <row r="95" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B95" s="20">
         <v>85</v>
       </c>
@@ -12393,7 +12587,7 @@
       </c>
       <c r="P95" s="22"/>
     </row>
-    <row r="96" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B96" s="20">
         <v>86</v>
       </c>
@@ -12424,7 +12618,7 @@
       </c>
       <c r="P96" s="22"/>
     </row>
-    <row r="97" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B97" s="20">
         <v>87</v>
       </c>
@@ -12455,7 +12649,7 @@
       </c>
       <c r="P97" s="22"/>
     </row>
-    <row r="98" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B98" s="20">
         <v>88</v>
       </c>
@@ -12486,7 +12680,7 @@
       </c>
       <c r="P98" s="22"/>
     </row>
-    <row r="99" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B99" s="20">
         <v>89</v>
       </c>
@@ -12517,7 +12711,7 @@
       </c>
       <c r="P99" s="22"/>
     </row>
-    <row r="100" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B100" s="20">
         <v>90</v>
       </c>
@@ -12548,7 +12742,7 @@
       </c>
       <c r="P100" s="22"/>
     </row>
-    <row r="101" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B101" s="20">
         <v>91</v>
       </c>
@@ -12579,7 +12773,7 @@
       </c>
       <c r="P101" s="22"/>
     </row>
-    <row r="102" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B102" s="20">
         <v>92</v>
       </c>
@@ -12610,7 +12804,7 @@
       </c>
       <c r="P102" s="22"/>
     </row>
-    <row r="103" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B103" s="20">
         <v>93</v>
       </c>
@@ -12641,7 +12835,7 @@
       </c>
       <c r="P103" s="22"/>
     </row>
-    <row r="104" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B104" s="20">
         <v>94</v>
       </c>
@@ -12672,7 +12866,7 @@
       </c>
       <c r="P104" s="22"/>
     </row>
-    <row r="105" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B105" s="20">
         <v>95</v>
       </c>
@@ -12703,7 +12897,7 @@
       </c>
       <c r="P105" s="22"/>
     </row>
-    <row r="106" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B106" s="20">
         <v>96</v>
       </c>
@@ -12734,7 +12928,7 @@
       </c>
       <c r="P106" s="22"/>
     </row>
-    <row r="107" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B107" s="20">
         <v>97</v>
       </c>
@@ -12765,7 +12959,7 @@
       </c>
       <c r="P107" s="22"/>
     </row>
-    <row r="108" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B108" s="20">
         <v>98</v>
       </c>
@@ -12796,7 +12990,7 @@
       </c>
       <c r="P108" s="22"/>
     </row>
-    <row r="109" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B109" s="20">
         <v>99</v>
       </c>
@@ -12827,7 +13021,7 @@
       </c>
       <c r="P109" s="22"/>
     </row>
-    <row r="110" spans="2:16" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:16" x14ac:dyDescent="0.3">
       <c r="B110" s="20">
         <v>100</v>
       </c>
@@ -12974,60 +13168,60 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B2:J39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="54" t="s">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B2" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="54"/>
-      <c r="F2" s="54"/>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-      <c r="J2" s="54"/>
-    </row>
-    <row r="4" spans="2:10" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="55" t="s">
+      <c r="C2" s="63"/>
+      <c r="D2" s="63"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
+      <c r="G2" s="63"/>
+      <c r="H2" s="63"/>
+      <c r="I2" s="63"/>
+      <c r="J2" s="63"/>
+    </row>
+    <row r="4" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="64" t="s">
         <v>89</v>
       </c>
-      <c r="C4" s="55"/>
-      <c r="D4" s="55"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="55"/>
-      <c r="G4" s="55"/>
-      <c r="H4" s="55"/>
-      <c r="I4" s="55"/>
-      <c r="J4" s="55"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
-      <c r="D5" s="55"/>
-      <c r="E5" s="55"/>
-      <c r="F5" s="55"/>
-      <c r="G5" s="55"/>
-      <c r="H5" s="55"/>
-      <c r="I5" s="55"/>
-      <c r="J5" s="55"/>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
-      <c r="D6" s="55"/>
-      <c r="E6" s="55"/>
-      <c r="F6" s="55"/>
-      <c r="G6" s="55"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="55"/>
-      <c r="J6" s="55"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
+      <c r="I4" s="64"/>
+      <c r="J4" s="64"/>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64"/>
+      <c r="F6" s="64"/>
+      <c r="G6" s="64"/>
+      <c r="H6" s="64"/>
+      <c r="I6" s="64"/>
+      <c r="J6" s="64"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
@@ -13038,7 +13232,7 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="29" t="s">
         <v>90</v>
       </c>
@@ -13051,7 +13245,7 @@
       <c r="I8" s="30"/>
       <c r="J8" s="30"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B9" s="31" t="s">
         <v>91</v>
       </c>
@@ -13064,7 +13258,7 @@
       <c r="I9" s="30"/>
       <c r="J9" s="30"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B10" s="31" t="s">
         <v>92</v>
       </c>
@@ -13077,7 +13271,7 @@
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B11" s="31" t="s">
         <v>31</v>
       </c>
@@ -13090,7 +13284,7 @@
       <c r="I11" s="30"/>
       <c r="J11" s="30"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B12" s="31" t="s">
         <v>36</v>
       </c>
@@ -13103,7 +13297,7 @@
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B13" s="31" t="s">
         <v>93</v>
       </c>
@@ -13116,7 +13310,7 @@
       <c r="I13" s="30"/>
       <c r="J13" s="30"/>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B14" s="32" t="s">
         <v>94</v>
       </c>
@@ -13129,7 +13323,7 @@
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B15" s="8"/>
       <c r="C15" s="30"/>
       <c r="D15" s="30"/>
@@ -13140,7 +13334,7 @@
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
@@ -13153,7 +13347,7 @@
       <c r="I16" s="30"/>
       <c r="J16" s="30"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B17" s="34" t="s">
         <v>96</v>
       </c>
@@ -13166,7 +13360,7 @@
       <c r="I17" s="30"/>
       <c r="J17" s="30"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B18" s="34" t="s">
         <v>97</v>
       </c>
@@ -13179,7 +13373,7 @@
       <c r="I18" s="30"/>
       <c r="J18" s="30"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B19" s="35" t="s">
         <v>98</v>
       </c>
@@ -13192,7 +13386,7 @@
       <c r="I19" s="30"/>
       <c r="J19" s="30"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B20" s="8"/>
       <c r="C20" s="30"/>
       <c r="D20" s="30"/>
@@ -13203,7 +13397,7 @@
       <c r="I20" s="30"/>
       <c r="J20" s="30"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B21" s="33" t="s">
         <v>99</v>
       </c>
@@ -13216,7 +13410,7 @@
       <c r="I21" s="30"/>
       <c r="J21" s="30"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B22" s="36">
         <v>45658</v>
       </c>
@@ -13229,7 +13423,7 @@
       <c r="I22" s="30"/>
       <c r="J22" s="30"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B23" s="37">
         <v>46062.354166666701</v>
       </c>
@@ -13242,7 +13436,7 @@
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B24" s="30"/>
       <c r="C24" s="30"/>
       <c r="D24" s="30"/>
@@ -13253,7 +13447,7 @@
       <c r="I24" s="30"/>
       <c r="J24" s="30"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B25" s="38" t="s">
         <v>100</v>
       </c>
@@ -13270,7 +13464,7 @@
       <c r="I25" s="40"/>
       <c r="J25" s="41"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B26" s="42" t="s">
         <v>76</v>
       </c>
@@ -13293,7 +13487,7 @@
       <c r="I26" s="30"/>
       <c r="J26" s="44"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B27" s="42" t="s">
         <v>45</v>
       </c>
@@ -13320,7 +13514,7 @@
       </c>
       <c r="J27" s="44"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B28" s="42" t="s">
         <v>73</v>
       </c>
@@ -13345,7 +13539,7 @@
       <c r="I28" s="30"/>
       <c r="J28" s="44"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B29" s="42" t="s">
         <v>37</v>
       </c>
@@ -13372,7 +13566,7 @@
       </c>
       <c r="J29" s="44"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B30" s="42" t="s">
         <v>56</v>
       </c>
@@ -13399,7 +13593,7 @@
       </c>
       <c r="J30" s="44"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B31" s="45" t="s">
         <v>32</v>
       </c>
@@ -13428,7 +13622,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B32" s="46" t="s">
         <v>115</v>
       </c>
@@ -13445,7 +13639,7 @@
       <c r="I32" s="48"/>
       <c r="J32" s="49"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B33" s="30"/>
       <c r="C33" s="30"/>
       <c r="D33" s="30"/>
@@ -13456,7 +13650,7 @@
       <c r="I33" s="30"/>
       <c r="J33" s="30"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B34" s="50" t="s">
         <v>116</v>
       </c>
@@ -13471,7 +13665,7 @@
       <c r="I34" s="30"/>
       <c r="J34" s="30"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B35" s="45" t="s">
         <v>30</v>
       </c>
@@ -13486,7 +13680,7 @@
       <c r="I35" s="30"/>
       <c r="J35" s="30"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B36" s="45" t="s">
         <v>35</v>
       </c>
@@ -13501,7 +13695,7 @@
       <c r="I36" s="30"/>
       <c r="J36" s="30"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B37" s="45" t="s">
         <v>55</v>
       </c>
@@ -13516,7 +13710,7 @@
       <c r="I37" s="30"/>
       <c r="J37" s="30"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B38" s="45" t="s">
         <v>72</v>
       </c>
@@ -13531,7 +13725,7 @@
       <c r="I38" s="30"/>
       <c r="J38" s="30"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B39" s="52" t="s">
         <v>115</v>
       </c>

--- a/Planning-Template.xlsx
+++ b/Planning-Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alvar\Desktop\DP2-2526\Workspace-26\Projects\Acme-Starters\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franr\OneDrive\Escritorio\informatica_us\asignaturas\DP2\ent\Workspace-26\Projects\Acme-Starters-B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CC2C1CD-94BA-4120-82C1-850708545C0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A258C7E-C0DA-46A2-AAD8-A6F2BD36B29A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5340" yWindow="-16320" windowWidth="38640" windowHeight="15720" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Copyright" sheetId="1" r:id="rId1"/>
@@ -46,8 +46,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="169">
   <si>
     <t>Copyright</t>
   </si>
@@ -537,15 +559,38 @@
   <si>
     <t>Redactar documento de Testing Report</t>
   </si>
+  <si>
+    <t>Escrbir requisitos elicitados en el analysis report</t>
+  </si>
+  <si>
+    <t>Definir tareas analizando API y posibilidades</t>
+  </si>
+  <si>
+    <t>T0002/M</t>
+  </si>
+  <si>
+    <t>Implementar conexión con jobicy</t>
+  </si>
+  <si>
+    <t>T0003/D</t>
+  </si>
+  <si>
+    <t>Comprobar funcionamiento correcto</t>
+  </si>
+  <si>
+    <t>Comprobar implementacion en follow up</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$EUR]\ #,##0.00"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy\ h:mm"/>
-    <numFmt numFmtId="166" formatCode="dd/mm/yyyy\ hh:mm"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -954,9 +999,9 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="11" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="6" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="22" fontId="6" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="12" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1732,12 +1777,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:AMJ12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1024" width="9.109375" style="2"/>
+    <col min="1" max="1024" width="9.08984375" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B2" s="63" t="s">
         <v>0</v>
       </c>
@@ -1750,7 +1795,7 @@
       <c r="I2" s="63"/>
       <c r="J2" s="63"/>
     </row>
-    <row r="4" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="64" t="s">
         <v>1</v>
       </c>
@@ -1763,7 +1808,7 @@
       <c r="I4" s="64"/>
       <c r="J4" s="64"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5" s="64"/>
       <c r="C5" s="64"/>
       <c r="D5" s="64"/>
@@ -1774,7 +1819,7 @@
       <c r="I5" s="64"/>
       <c r="J5" s="64"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6" s="64"/>
       <c r="C6" s="64"/>
       <c r="D6" s="64"/>
@@ -1785,7 +1830,7 @@
       <c r="I6" s="64"/>
       <c r="J6" s="64"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7" s="64"/>
       <c r="C7" s="64"/>
       <c r="D7" s="64"/>
@@ -1796,7 +1841,7 @@
       <c r="I7" s="64"/>
       <c r="J7" s="64"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B8" s="64"/>
       <c r="C8" s="64"/>
       <c r="D8" s="64"/>
@@ -1807,7 +1852,7 @@
       <c r="I8" s="64"/>
       <c r="J8" s="64"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9" s="64"/>
       <c r="C9" s="64"/>
       <c r="D9" s="64"/>
@@ -1818,7 +1863,7 @@
       <c r="I9" s="64"/>
       <c r="J9" s="64"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B10" s="64"/>
       <c r="C10" s="64"/>
       <c r="D10" s="64"/>
@@ -1829,7 +1874,7 @@
       <c r="I10" s="64"/>
       <c r="J10" s="64"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11" s="64"/>
       <c r="C11" s="64"/>
       <c r="D11" s="64"/>
@@ -1840,7 +1885,7 @@
       <c r="I11" s="64"/>
       <c r="J11" s="64"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B12" s="64"/>
       <c r="C12" s="64"/>
       <c r="D12" s="64"/>
@@ -1865,9 +1910,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:J12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B2" s="63" t="s">
         <v>2</v>
       </c>
@@ -1880,7 +1925,7 @@
       <c r="I2" s="63"/>
       <c r="J2" s="63"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B3" s="3"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
@@ -1891,7 +1936,7 @@
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
     </row>
-    <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="64" t="s">
         <v>3</v>
       </c>
@@ -1904,7 +1949,7 @@
       <c r="I4" s="64"/>
       <c r="J4" s="64"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5" s="64"/>
       <c r="C5" s="64"/>
       <c r="D5" s="64"/>
@@ -1915,7 +1960,7 @@
       <c r="I5" s="64"/>
       <c r="J5" s="64"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6" s="64"/>
       <c r="C6" s="64"/>
       <c r="D6" s="64"/>
@@ -1926,7 +1971,7 @@
       <c r="I6" s="64"/>
       <c r="J6" s="64"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
@@ -1937,7 +1982,7 @@
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B8" s="4"/>
       <c r="C8" s="2" t="s">
         <v>4</v>
@@ -1950,7 +1995,7 @@
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9" s="5"/>
       <c r="C9" s="67" t="s">
         <v>5</v>
@@ -1963,7 +2008,7 @@
       <c r="I9" s="67"/>
       <c r="J9" s="67"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B10" s="6"/>
       <c r="C10" s="67" t="s">
         <v>6</v>
@@ -1976,7 +2021,7 @@
       <c r="I10" s="67"/>
       <c r="J10" s="67"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11" s="7"/>
       <c r="C11" s="1" t="s">
         <v>7</v>
@@ -1989,7 +2034,7 @@
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B12" s="8"/>
       <c r="C12" s="67" t="s">
         <v>8</v>
@@ -2018,16 +2063,16 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:P110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="6" width="18.88671875" customWidth="1"/>
-    <col min="7" max="7" width="23.44140625" customWidth="1"/>
-    <col min="8" max="8" width="13.5546875" customWidth="1"/>
-    <col min="9" max="15" width="18.88671875" customWidth="1"/>
-    <col min="16" max="16" width="64.5546875" customWidth="1"/>
+    <col min="3" max="6" width="18.90625" customWidth="1"/>
+    <col min="7" max="7" width="23.453125" customWidth="1"/>
+    <col min="8" max="8" width="13.54296875" customWidth="1"/>
+    <col min="9" max="15" width="18.90625" customWidth="1"/>
+    <col min="16" max="16" width="64.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C2" s="63" t="s">
         <v>9</v>
       </c>
@@ -2045,7 +2090,7 @@
       <c r="O2" s="63"/>
       <c r="P2" s="63"/>
     </row>
-    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C4" s="64" t="s">
         <v>10</v>
       </c>
@@ -2063,7 +2108,7 @@
       <c r="O4" s="64"/>
       <c r="P4" s="64"/>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -2079,7 +2124,7 @@
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
     </row>
-    <row r="6" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C6" s="65" t="s">
         <v>11</v>
       </c>
@@ -2102,7 +2147,7 @@
       <c r="O6" s="9"/>
       <c r="P6" s="9"/>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C7" s="65"/>
       <c r="D7" s="12" t="s">
         <v>13</v>
@@ -2113,7 +2158,7 @@
       </c>
       <c r="J7" s="14"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B9" s="15"/>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
@@ -2136,7 +2181,7 @@
       <c r="O9" s="66"/>
       <c r="P9" s="16"/>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B10" s="53" t="s">
         <v>17</v>
       </c>
@@ -2183,7 +2228,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B11" s="20">
         <v>1</v>
       </c>
@@ -2232,7 +2277,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B12" s="20">
         <v>2</v>
       </c>
@@ -2281,7 +2326,7 @@
       </c>
       <c r="P12" s="22"/>
     </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B13" s="20">
         <v>3</v>
       </c>
@@ -2332,7 +2377,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B14" s="20">
         <v>4</v>
       </c>
@@ -2382,7 +2427,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B15" s="20">
         <v>5</v>
       </c>
@@ -2431,7 +2476,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B16" s="20">
         <v>6</v>
       </c>
@@ -2482,7 +2527,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B17" s="20">
         <v>7</v>
       </c>
@@ -2533,7 +2578,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B18" s="20">
         <v>8</v>
       </c>
@@ -2584,7 +2629,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B19" s="20">
         <v>9</v>
       </c>
@@ -2635,7 +2680,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B20" s="20">
         <v>10</v>
       </c>
@@ -2686,7 +2731,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B21" s="20">
         <v>11</v>
       </c>
@@ -2737,7 +2782,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B22" s="20">
         <v>12</v>
       </c>
@@ -2788,7 +2833,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B23" s="20">
         <v>13</v>
       </c>
@@ -2837,7 +2882,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B24" s="20">
         <v>14</v>
       </c>
@@ -2888,7 +2933,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B25" s="20">
         <v>15</v>
       </c>
@@ -2939,7 +2984,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B26" s="20">
         <v>16</v>
       </c>
@@ -2987,7 +3032,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B27" s="20">
         <v>17</v>
       </c>
@@ -3036,7 +3081,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B28" s="20">
         <v>18</v>
       </c>
@@ -3085,7 +3130,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B29" s="20">
         <v>19</v>
       </c>
@@ -3134,7 +3179,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B30" s="20">
         <v>20</v>
       </c>
@@ -3183,7 +3228,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B31" s="20">
         <v>21</v>
       </c>
@@ -3232,7 +3277,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B32" s="20">
         <v>22</v>
       </c>
@@ -3281,7 +3326,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B33" s="20">
         <v>23</v>
       </c>
@@ -3330,7 +3375,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="34" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B34" s="20">
         <v>24</v>
       </c>
@@ -3379,7 +3424,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="35" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B35" s="20">
         <v>25</v>
       </c>
@@ -3427,7 +3472,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B36" s="20">
         <v>26</v>
       </c>
@@ -3477,7 +3522,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B37" s="20">
         <v>27</v>
       </c>
@@ -3525,7 +3570,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B38" s="20">
         <v>28</v>
       </c>
@@ -3575,7 +3620,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B39" s="20">
         <v>29</v>
       </c>
@@ -3625,7 +3670,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B40" s="20">
         <v>30</v>
       </c>
@@ -3675,7 +3720,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B41" s="20">
         <v>31</v>
       </c>
@@ -3725,7 +3770,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B42" s="20">
         <v>32</v>
       </c>
@@ -3775,7 +3820,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B43" s="20">
         <v>33</v>
       </c>
@@ -3825,7 +3870,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="44" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B44" s="20">
         <v>34</v>
       </c>
@@ -3873,7 +3918,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="45" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B45" s="20">
         <v>35</v>
       </c>
@@ -3921,7 +3966,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="46" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B46" s="20">
         <v>36</v>
       </c>
@@ -3969,7 +4014,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="47" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B47" s="20">
         <v>37</v>
       </c>
@@ -4017,7 +4062,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="48" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B48" s="20">
         <v>38</v>
       </c>
@@ -4065,7 +4110,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="49" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B49" s="20">
         <v>39</v>
       </c>
@@ -4113,7 +4158,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="50" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B50" s="20">
         <v>40</v>
       </c>
@@ -4161,7 +4206,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="51" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B51" s="20">
         <v>41</v>
       </c>
@@ -4209,7 +4254,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B52" s="20">
         <v>42</v>
       </c>
@@ -4237,7 +4282,7 @@
       </c>
       <c r="P52" s="22"/>
     </row>
-    <row r="53" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B53" s="20">
         <v>43</v>
       </c>
@@ -4268,7 +4313,7 @@
       </c>
       <c r="P53" s="22"/>
     </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B54" s="20">
         <v>44</v>
       </c>
@@ -4299,7 +4344,7 @@
       </c>
       <c r="P54" s="22"/>
     </row>
-    <row r="55" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B55" s="20">
         <v>45</v>
       </c>
@@ -4330,7 +4375,7 @@
       </c>
       <c r="P55" s="22"/>
     </row>
-    <row r="56" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B56" s="20">
         <v>46</v>
       </c>
@@ -4361,7 +4406,7 @@
       </c>
       <c r="P56" s="22"/>
     </row>
-    <row r="57" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B57" s="20">
         <v>47</v>
       </c>
@@ -4392,7 +4437,7 @@
       </c>
       <c r="P57" s="22"/>
     </row>
-    <row r="58" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B58" s="20">
         <v>48</v>
       </c>
@@ -4423,7 +4468,7 @@
       </c>
       <c r="P58" s="22"/>
     </row>
-    <row r="59" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B59" s="20">
         <v>49</v>
       </c>
@@ -4454,7 +4499,7 @@
       </c>
       <c r="P59" s="22"/>
     </row>
-    <row r="60" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B60" s="20">
         <v>50</v>
       </c>
@@ -4485,7 +4530,7 @@
       </c>
       <c r="P60" s="22"/>
     </row>
-    <row r="61" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B61" s="20">
         <v>51</v>
       </c>
@@ -4516,7 +4561,7 @@
       </c>
       <c r="P61" s="22"/>
     </row>
-    <row r="62" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B62" s="20">
         <v>52</v>
       </c>
@@ -4547,7 +4592,7 @@
       </c>
       <c r="P62" s="22"/>
     </row>
-    <row r="63" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B63" s="20">
         <v>53</v>
       </c>
@@ -4578,7 +4623,7 @@
       </c>
       <c r="P63" s="22"/>
     </row>
-    <row r="64" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B64" s="20">
         <v>54</v>
       </c>
@@ -4609,7 +4654,7 @@
       </c>
       <c r="P64" s="22"/>
     </row>
-    <row r="65" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B65" s="20">
         <v>55</v>
       </c>
@@ -4640,7 +4685,7 @@
       </c>
       <c r="P65" s="22"/>
     </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B66" s="20">
         <v>56</v>
       </c>
@@ -4671,7 +4716,7 @@
       </c>
       <c r="P66" s="22"/>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B67" s="20">
         <v>57</v>
       </c>
@@ -4702,7 +4747,7 @@
       </c>
       <c r="P67" s="22"/>
     </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B68" s="20">
         <v>58</v>
       </c>
@@ -4733,7 +4778,7 @@
       </c>
       <c r="P68" s="22"/>
     </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B69" s="20">
         <v>59</v>
       </c>
@@ -4764,7 +4809,7 @@
       </c>
       <c r="P69" s="22"/>
     </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B70" s="20">
         <v>60</v>
       </c>
@@ -4795,7 +4840,7 @@
       </c>
       <c r="P70" s="22"/>
     </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B71" s="20">
         <v>61</v>
       </c>
@@ -4826,7 +4871,7 @@
       </c>
       <c r="P71" s="22"/>
     </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B72" s="20">
         <v>62</v>
       </c>
@@ -4857,7 +4902,7 @@
       </c>
       <c r="P72" s="22"/>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B73" s="20">
         <v>63</v>
       </c>
@@ -4888,7 +4933,7 @@
       </c>
       <c r="P73" s="22"/>
     </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B74" s="20">
         <v>64</v>
       </c>
@@ -4919,7 +4964,7 @@
       </c>
       <c r="P74" s="22"/>
     </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B75" s="20">
         <v>65</v>
       </c>
@@ -4950,7 +4995,7 @@
       </c>
       <c r="P75" s="22"/>
     </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B76" s="20">
         <v>66</v>
       </c>
@@ -4981,7 +5026,7 @@
       </c>
       <c r="P76" s="22"/>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B77" s="20">
         <v>67</v>
       </c>
@@ -5012,7 +5057,7 @@
       </c>
       <c r="P77" s="22"/>
     </row>
-    <row r="78" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B78" s="20">
         <v>68</v>
       </c>
@@ -5043,7 +5088,7 @@
       </c>
       <c r="P78" s="22"/>
     </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B79" s="20">
         <v>69</v>
       </c>
@@ -5074,7 +5119,7 @@
       </c>
       <c r="P79" s="22"/>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B80" s="20">
         <v>70</v>
       </c>
@@ -5105,7 +5150,7 @@
       </c>
       <c r="P80" s="22"/>
     </row>
-    <row r="81" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B81" s="20">
         <v>71</v>
       </c>
@@ -5136,7 +5181,7 @@
       </c>
       <c r="P81" s="22"/>
     </row>
-    <row r="82" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B82" s="20">
         <v>72</v>
       </c>
@@ -5167,7 +5212,7 @@
       </c>
       <c r="P82" s="22"/>
     </row>
-    <row r="83" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B83" s="20">
         <v>73</v>
       </c>
@@ -5198,7 +5243,7 @@
       </c>
       <c r="P83" s="22"/>
     </row>
-    <row r="84" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B84" s="20">
         <v>74</v>
       </c>
@@ -5229,7 +5274,7 @@
       </c>
       <c r="P84" s="22"/>
     </row>
-    <row r="85" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B85" s="20">
         <v>75</v>
       </c>
@@ -5260,7 +5305,7 @@
       </c>
       <c r="P85" s="22"/>
     </row>
-    <row r="86" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B86" s="20">
         <v>76</v>
       </c>
@@ -5291,7 +5336,7 @@
       </c>
       <c r="P86" s="22"/>
     </row>
-    <row r="87" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B87" s="20">
         <v>77</v>
       </c>
@@ -5322,7 +5367,7 @@
       </c>
       <c r="P87" s="22"/>
     </row>
-    <row r="88" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B88" s="20">
         <v>78</v>
       </c>
@@ -5353,7 +5398,7 @@
       </c>
       <c r="P88" s="22"/>
     </row>
-    <row r="89" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B89" s="20">
         <v>79</v>
       </c>
@@ -5384,7 +5429,7 @@
       </c>
       <c r="P89" s="22"/>
     </row>
-    <row r="90" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B90" s="20">
         <v>80</v>
       </c>
@@ -5415,7 +5460,7 @@
       </c>
       <c r="P90" s="22"/>
     </row>
-    <row r="91" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B91" s="20">
         <v>81</v>
       </c>
@@ -5446,7 +5491,7 @@
       </c>
       <c r="P91" s="22"/>
     </row>
-    <row r="92" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B92" s="20">
         <v>82</v>
       </c>
@@ -5477,7 +5522,7 @@
       </c>
       <c r="P92" s="22"/>
     </row>
-    <row r="93" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B93" s="20">
         <v>83</v>
       </c>
@@ -5508,7 +5553,7 @@
       </c>
       <c r="P93" s="22"/>
     </row>
-    <row r="94" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B94" s="20">
         <v>84</v>
       </c>
@@ -5539,7 +5584,7 @@
       </c>
       <c r="P94" s="22"/>
     </row>
-    <row r="95" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B95" s="20">
         <v>85</v>
       </c>
@@ -5570,7 +5615,7 @@
       </c>
       <c r="P95" s="22"/>
     </row>
-    <row r="96" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B96" s="20">
         <v>86</v>
       </c>
@@ -5601,7 +5646,7 @@
       </c>
       <c r="P96" s="22"/>
     </row>
-    <row r="97" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B97" s="20">
         <v>87</v>
       </c>
@@ -5632,7 +5677,7 @@
       </c>
       <c r="P97" s="22"/>
     </row>
-    <row r="98" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B98" s="20">
         <v>88</v>
       </c>
@@ -5663,7 +5708,7 @@
       </c>
       <c r="P98" s="22"/>
     </row>
-    <row r="99" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B99" s="20">
         <v>89</v>
       </c>
@@ -5694,7 +5739,7 @@
       </c>
       <c r="P99" s="22"/>
     </row>
-    <row r="100" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B100" s="20">
         <v>90</v>
       </c>
@@ -5725,7 +5770,7 @@
       </c>
       <c r="P100" s="22"/>
     </row>
-    <row r="101" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B101" s="20">
         <v>91</v>
       </c>
@@ -5756,7 +5801,7 @@
       </c>
       <c r="P101" s="22"/>
     </row>
-    <row r="102" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B102" s="20">
         <v>92</v>
       </c>
@@ -5787,7 +5832,7 @@
       </c>
       <c r="P102" s="22"/>
     </row>
-    <row r="103" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B103" s="20">
         <v>93</v>
       </c>
@@ -5818,7 +5863,7 @@
       </c>
       <c r="P103" s="22"/>
     </row>
-    <row r="104" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B104" s="20">
         <v>94</v>
       </c>
@@ -5849,7 +5894,7 @@
       </c>
       <c r="P104" s="22"/>
     </row>
-    <row r="105" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B105" s="20">
         <v>95</v>
       </c>
@@ -5880,7 +5925,7 @@
       </c>
       <c r="P105" s="22"/>
     </row>
-    <row r="106" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B106" s="20">
         <v>96</v>
       </c>
@@ -5911,7 +5956,7 @@
       </c>
       <c r="P106" s="22"/>
     </row>
-    <row r="107" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B107" s="20">
         <v>97</v>
       </c>
@@ -5942,7 +5987,7 @@
       </c>
       <c r="P107" s="22"/>
     </row>
-    <row r="108" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B108" s="20">
         <v>98</v>
       </c>
@@ -5973,7 +6018,7 @@
       </c>
       <c r="P108" s="22"/>
     </row>
-    <row r="109" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B109" s="20">
         <v>99</v>
       </c>
@@ -6004,7 +6049,7 @@
       </c>
       <c r="P109" s="22"/>
     </row>
-    <row r="110" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B110" s="20">
         <v>100</v>
       </c>
@@ -6143,13 +6188,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B2:P110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="15" width="18.88671875" customWidth="1"/>
-    <col min="16" max="16" width="64.5546875" customWidth="1"/>
+    <col min="3" max="15" width="18.90625" customWidth="1"/>
+    <col min="16" max="16" width="64.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C2" s="63" t="s">
         <v>71</v>
       </c>
@@ -6167,7 +6212,7 @@
       <c r="O2" s="63"/>
       <c r="P2" s="63"/>
     </row>
-    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C4" s="64" t="s">
         <v>10</v>
       </c>
@@ -6185,7 +6230,7 @@
       <c r="O4" s="64"/>
       <c r="P4" s="64"/>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -6201,7 +6246,7 @@
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
     </row>
-    <row r="6" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C6" s="65" t="s">
         <v>11</v>
       </c>
@@ -6224,7 +6269,7 @@
       <c r="O6" s="9"/>
       <c r="P6" s="9"/>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:16" x14ac:dyDescent="0.35">
       <c r="C7" s="65"/>
       <c r="D7" s="12" t="s">
         <v>13</v>
@@ -6235,7 +6280,7 @@
       </c>
       <c r="J7" s="14"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B9" s="15"/>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
@@ -6258,7 +6303,7 @@
       <c r="O9" s="66"/>
       <c r="P9" s="16"/>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B10" s="17" t="s">
         <v>17</v>
       </c>
@@ -6305,7 +6350,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B11" s="20">
         <v>1</v>
       </c>
@@ -6354,7 +6399,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B12" s="20">
         <v>2</v>
       </c>
@@ -6403,7 +6448,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B13" s="20">
         <v>3</v>
       </c>
@@ -6454,7 +6499,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B14" s="20">
         <v>4</v>
       </c>
@@ -6505,7 +6550,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B15" s="20">
         <v>5</v>
       </c>
@@ -6556,7 +6601,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B16" s="20">
         <v>6</v>
       </c>
@@ -6607,7 +6652,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B17" s="20">
         <v>7</v>
       </c>
@@ -6656,7 +6701,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B18" s="20">
         <v>8</v>
       </c>
@@ -6705,7 +6750,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B19" s="20">
         <v>9</v>
       </c>
@@ -6754,7 +6799,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B20" s="20">
         <v>10</v>
       </c>
@@ -6803,7 +6848,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B21" s="20">
         <v>11</v>
       </c>
@@ -6852,7 +6897,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B22" s="20">
         <v>12</v>
       </c>
@@ -6901,7 +6946,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B23" s="20">
         <v>13</v>
       </c>
@@ -6950,7 +6995,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B24" s="20">
         <v>14</v>
       </c>
@@ -6999,7 +7044,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B25" s="20">
         <v>15</v>
       </c>
@@ -7048,7 +7093,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B26" s="20">
         <v>16</v>
       </c>
@@ -7079,7 +7124,7 @@
       </c>
       <c r="P26" s="22"/>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B27" s="20">
         <v>17</v>
       </c>
@@ -7110,7 +7155,7 @@
       </c>
       <c r="P27" s="22"/>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B28" s="20">
         <v>18</v>
       </c>
@@ -7141,7 +7186,7 @@
       </c>
       <c r="P28" s="22"/>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B29" s="20">
         <v>19</v>
       </c>
@@ -7172,7 +7217,7 @@
       </c>
       <c r="P29" s="22"/>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B30" s="20">
         <v>20</v>
       </c>
@@ -7203,7 +7248,7 @@
       </c>
       <c r="P30" s="22"/>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B31" s="20">
         <v>21</v>
       </c>
@@ -7234,7 +7279,7 @@
       </c>
       <c r="P31" s="22"/>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B32" s="20">
         <v>22</v>
       </c>
@@ -7265,7 +7310,7 @@
       </c>
       <c r="P32" s="22"/>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B33" s="20">
         <v>23</v>
       </c>
@@ -7296,7 +7341,7 @@
       </c>
       <c r="P33" s="22"/>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B34" s="20">
         <v>24</v>
       </c>
@@ -7327,7 +7372,7 @@
       </c>
       <c r="P34" s="22"/>
     </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B35" s="20">
         <v>25</v>
       </c>
@@ -7358,7 +7403,7 @@
       </c>
       <c r="P35" s="22"/>
     </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B36" s="20">
         <v>26</v>
       </c>
@@ -7389,7 +7434,7 @@
       </c>
       <c r="P36" s="22"/>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B37" s="20">
         <v>27</v>
       </c>
@@ -7420,7 +7465,7 @@
       </c>
       <c r="P37" s="22"/>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B38" s="20">
         <v>28</v>
       </c>
@@ -7451,7 +7496,7 @@
       </c>
       <c r="P38" s="22"/>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B39" s="20">
         <v>29</v>
       </c>
@@ -7482,7 +7527,7 @@
       </c>
       <c r="P39" s="22"/>
     </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B40" s="20">
         <v>30</v>
       </c>
@@ -7513,7 +7558,7 @@
       </c>
       <c r="P40" s="22"/>
     </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B41" s="20">
         <v>31</v>
       </c>
@@ -7544,7 +7589,7 @@
       </c>
       <c r="P41" s="22"/>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B42" s="20">
         <v>32</v>
       </c>
@@ -7575,7 +7620,7 @@
       </c>
       <c r="P42" s="22"/>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B43" s="20">
         <v>33</v>
       </c>
@@ -7606,7 +7651,7 @@
       </c>
       <c r="P43" s="22"/>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B44" s="20">
         <v>34</v>
       </c>
@@ -7637,7 +7682,7 @@
       </c>
       <c r="P44" s="22"/>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B45" s="20">
         <v>35</v>
       </c>
@@ -7668,7 +7713,7 @@
       </c>
       <c r="P45" s="22"/>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B46" s="20">
         <v>36</v>
       </c>
@@ -7699,7 +7744,7 @@
       </c>
       <c r="P46" s="22"/>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B47" s="20">
         <v>37</v>
       </c>
@@ -7730,7 +7775,7 @@
       </c>
       <c r="P47" s="22"/>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B48" s="20">
         <v>38</v>
       </c>
@@ -7761,7 +7806,7 @@
       </c>
       <c r="P48" s="22"/>
     </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B49" s="20">
         <v>39</v>
       </c>
@@ -7792,7 +7837,7 @@
       </c>
       <c r="P49" s="22"/>
     </row>
-    <row r="50" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B50" s="20">
         <v>40</v>
       </c>
@@ -7823,7 +7868,7 @@
       </c>
       <c r="P50" s="22"/>
     </row>
-    <row r="51" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B51" s="20">
         <v>41</v>
       </c>
@@ -7854,7 +7899,7 @@
       </c>
       <c r="P51" s="22"/>
     </row>
-    <row r="52" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B52" s="20">
         <v>42</v>
       </c>
@@ -7885,7 +7930,7 @@
       </c>
       <c r="P52" s="22"/>
     </row>
-    <row r="53" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B53" s="20">
         <v>43</v>
       </c>
@@ -7916,7 +7961,7 @@
       </c>
       <c r="P53" s="22"/>
     </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B54" s="20">
         <v>44</v>
       </c>
@@ -7947,7 +7992,7 @@
       </c>
       <c r="P54" s="22"/>
     </row>
-    <row r="55" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B55" s="20">
         <v>45</v>
       </c>
@@ -7978,7 +8023,7 @@
       </c>
       <c r="P55" s="22"/>
     </row>
-    <row r="56" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B56" s="20">
         <v>46</v>
       </c>
@@ -8009,7 +8054,7 @@
       </c>
       <c r="P56" s="22"/>
     </row>
-    <row r="57" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B57" s="20">
         <v>47</v>
       </c>
@@ -8040,7 +8085,7 @@
       </c>
       <c r="P57" s="22"/>
     </row>
-    <row r="58" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B58" s="20">
         <v>48</v>
       </c>
@@ -8071,7 +8116,7 @@
       </c>
       <c r="P58" s="22"/>
     </row>
-    <row r="59" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B59" s="20">
         <v>49</v>
       </c>
@@ -8102,7 +8147,7 @@
       </c>
       <c r="P59" s="22"/>
     </row>
-    <row r="60" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B60" s="20">
         <v>50</v>
       </c>
@@ -8133,7 +8178,7 @@
       </c>
       <c r="P60" s="22"/>
     </row>
-    <row r="61" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B61" s="20">
         <v>51</v>
       </c>
@@ -8164,7 +8209,7 @@
       </c>
       <c r="P61" s="22"/>
     </row>
-    <row r="62" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B62" s="20">
         <v>52</v>
       </c>
@@ -8195,7 +8240,7 @@
       </c>
       <c r="P62" s="22"/>
     </row>
-    <row r="63" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B63" s="20">
         <v>53</v>
       </c>
@@ -8226,7 +8271,7 @@
       </c>
       <c r="P63" s="22"/>
     </row>
-    <row r="64" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B64" s="20">
         <v>54</v>
       </c>
@@ -8257,7 +8302,7 @@
       </c>
       <c r="P64" s="22"/>
     </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B65" s="20">
         <v>55</v>
       </c>
@@ -8288,7 +8333,7 @@
       </c>
       <c r="P65" s="22"/>
     </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B66" s="20">
         <v>56</v>
       </c>
@@ -8319,7 +8364,7 @@
       </c>
       <c r="P66" s="22"/>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B67" s="20">
         <v>57</v>
       </c>
@@ -8350,7 +8395,7 @@
       </c>
       <c r="P67" s="22"/>
     </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B68" s="20">
         <v>58</v>
       </c>
@@ -8381,7 +8426,7 @@
       </c>
       <c r="P68" s="22"/>
     </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B69" s="20">
         <v>59</v>
       </c>
@@ -8412,7 +8457,7 @@
       </c>
       <c r="P69" s="22"/>
     </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B70" s="20">
         <v>60</v>
       </c>
@@ -8443,7 +8488,7 @@
       </c>
       <c r="P70" s="22"/>
     </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B71" s="20">
         <v>61</v>
       </c>
@@ -8474,7 +8519,7 @@
       </c>
       <c r="P71" s="22"/>
     </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B72" s="20">
         <v>62</v>
       </c>
@@ -8505,7 +8550,7 @@
       </c>
       <c r="P72" s="22"/>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B73" s="20">
         <v>63</v>
       </c>
@@ -8536,7 +8581,7 @@
       </c>
       <c r="P73" s="22"/>
     </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B74" s="20">
         <v>64</v>
       </c>
@@ -8567,7 +8612,7 @@
       </c>
       <c r="P74" s="22"/>
     </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B75" s="20">
         <v>65</v>
       </c>
@@ -8598,7 +8643,7 @@
       </c>
       <c r="P75" s="22"/>
     </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B76" s="20">
         <v>66</v>
       </c>
@@ -8629,7 +8674,7 @@
       </c>
       <c r="P76" s="22"/>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B77" s="20">
         <v>67</v>
       </c>
@@ -8660,7 +8705,7 @@
       </c>
       <c r="P77" s="22"/>
     </row>
-    <row r="78" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B78" s="20">
         <v>68</v>
       </c>
@@ -8691,7 +8736,7 @@
       </c>
       <c r="P78" s="22"/>
     </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B79" s="20">
         <v>69</v>
       </c>
@@ -8722,7 +8767,7 @@
       </c>
       <c r="P79" s="22"/>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B80" s="20">
         <v>70</v>
       </c>
@@ -8753,7 +8798,7 @@
       </c>
       <c r="P80" s="22"/>
     </row>
-    <row r="81" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B81" s="20">
         <v>71</v>
       </c>
@@ -8784,7 +8829,7 @@
       </c>
       <c r="P81" s="22"/>
     </row>
-    <row r="82" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B82" s="20">
         <v>72</v>
       </c>
@@ -8815,7 +8860,7 @@
       </c>
       <c r="P82" s="22"/>
     </row>
-    <row r="83" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B83" s="20">
         <v>73</v>
       </c>
@@ -8846,7 +8891,7 @@
       </c>
       <c r="P83" s="22"/>
     </row>
-    <row r="84" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B84" s="20">
         <v>74</v>
       </c>
@@ -8877,7 +8922,7 @@
       </c>
       <c r="P84" s="22"/>
     </row>
-    <row r="85" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B85" s="20">
         <v>75</v>
       </c>
@@ -8908,7 +8953,7 @@
       </c>
       <c r="P85" s="22"/>
     </row>
-    <row r="86" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B86" s="20">
         <v>76</v>
       </c>
@@ -8939,7 +8984,7 @@
       </c>
       <c r="P86" s="22"/>
     </row>
-    <row r="87" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B87" s="20">
         <v>77</v>
       </c>
@@ -8970,7 +9015,7 @@
       </c>
       <c r="P87" s="22"/>
     </row>
-    <row r="88" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B88" s="20">
         <v>78</v>
       </c>
@@ -9001,7 +9046,7 @@
       </c>
       <c r="P88" s="22"/>
     </row>
-    <row r="89" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B89" s="20">
         <v>79</v>
       </c>
@@ -9032,7 +9077,7 @@
       </c>
       <c r="P89" s="22"/>
     </row>
-    <row r="90" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B90" s="20">
         <v>80</v>
       </c>
@@ -9063,7 +9108,7 @@
       </c>
       <c r="P90" s="22"/>
     </row>
-    <row r="91" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B91" s="20">
         <v>81</v>
       </c>
@@ -9094,7 +9139,7 @@
       </c>
       <c r="P91" s="22"/>
     </row>
-    <row r="92" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B92" s="20">
         <v>82</v>
       </c>
@@ -9125,7 +9170,7 @@
       </c>
       <c r="P92" s="22"/>
     </row>
-    <row r="93" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B93" s="20">
         <v>83</v>
       </c>
@@ -9156,7 +9201,7 @@
       </c>
       <c r="P93" s="22"/>
     </row>
-    <row r="94" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B94" s="20">
         <v>84</v>
       </c>
@@ -9187,7 +9232,7 @@
       </c>
       <c r="P94" s="22"/>
     </row>
-    <row r="95" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B95" s="20">
         <v>85</v>
       </c>
@@ -9218,7 +9263,7 @@
       </c>
       <c r="P95" s="22"/>
     </row>
-    <row r="96" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B96" s="20">
         <v>86</v>
       </c>
@@ -9249,7 +9294,7 @@
       </c>
       <c r="P96" s="22"/>
     </row>
-    <row r="97" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B97" s="20">
         <v>87</v>
       </c>
@@ -9280,7 +9325,7 @@
       </c>
       <c r="P97" s="22"/>
     </row>
-    <row r="98" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B98" s="20">
         <v>88</v>
       </c>
@@ -9311,7 +9356,7 @@
       </c>
       <c r="P98" s="22"/>
     </row>
-    <row r="99" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B99" s="20">
         <v>89</v>
       </c>
@@ -9342,7 +9387,7 @@
       </c>
       <c r="P99" s="22"/>
     </row>
-    <row r="100" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B100" s="20">
         <v>90</v>
       </c>
@@ -9373,7 +9418,7 @@
       </c>
       <c r="P100" s="22"/>
     </row>
-    <row r="101" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B101" s="20">
         <v>91</v>
       </c>
@@ -9404,7 +9449,7 @@
       </c>
       <c r="P101" s="22"/>
     </row>
-    <row r="102" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B102" s="20">
         <v>92</v>
       </c>
@@ -9435,7 +9480,7 @@
       </c>
       <c r="P102" s="22"/>
     </row>
-    <row r="103" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B103" s="20">
         <v>93</v>
       </c>
@@ -9466,7 +9511,7 @@
       </c>
       <c r="P103" s="22"/>
     </row>
-    <row r="104" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B104" s="20">
         <v>94</v>
       </c>
@@ -9497,7 +9542,7 @@
       </c>
       <c r="P104" s="22"/>
     </row>
-    <row r="105" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B105" s="20">
         <v>95</v>
       </c>
@@ -9528,7 +9573,7 @@
       </c>
       <c r="P105" s="22"/>
     </row>
-    <row r="106" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B106" s="20">
         <v>96</v>
       </c>
@@ -9559,7 +9604,7 @@
       </c>
       <c r="P106" s="22"/>
     </row>
-    <row r="107" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B107" s="20">
         <v>97</v>
       </c>
@@ -9590,7 +9635,7 @@
       </c>
       <c r="P107" s="22"/>
     </row>
-    <row r="108" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B108" s="20">
         <v>98</v>
       </c>
@@ -9621,7 +9666,7 @@
       </c>
       <c r="P108" s="22"/>
     </row>
-    <row r="109" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B109" s="20">
         <v>99</v>
       </c>
@@ -9652,7 +9697,7 @@
       </c>
       <c r="P109" s="22"/>
     </row>
-    <row r="110" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B110" s="20">
         <v>100</v>
       </c>
@@ -9789,14 +9834,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="B2:P110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:P110"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="15" width="18.88671875" customWidth="1"/>
-    <col min="16" max="16" width="64.5546875" customWidth="1"/>
+    <col min="3" max="15" width="18.90625" customWidth="1"/>
+    <col min="16" max="16" width="64.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="C2" s="63" t="s">
         <v>87</v>
       </c>
@@ -9814,7 +9859,7 @@
       <c r="O2" s="63"/>
       <c r="P2" s="63"/>
     </row>
-    <row r="4" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="C4" s="64" t="s">
         <v>10</v>
       </c>
@@ -9832,7 +9877,7 @@
       <c r="O4" s="64"/>
       <c r="P4" s="64"/>
     </row>
-    <row r="5" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
@@ -9848,7 +9893,11 @@
       <c r="O5" s="9"/>
       <c r="P5" s="9"/>
     </row>
-    <row r="6" spans="2:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B6" cm="1">
+        <f t="array" aca="1" ref="B6" ca="1">B6:P15</f>
+        <v>0</v>
+      </c>
       <c r="C6" s="65" t="s">
         <v>11</v>
       </c>
@@ -9857,7 +9906,7 @@
       </c>
       <c r="E6" s="11">
         <f>SUM(N11:N110)</f>
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
@@ -9871,18 +9920,18 @@
       <c r="O6" s="9"/>
       <c r="P6" s="9"/>
     </row>
-    <row r="7" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="C7" s="65"/>
       <c r="D7" s="12" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="13">
         <f>SUM(O11:O110)</f>
-        <v>0</v>
+        <v>255</v>
       </c>
       <c r="J7" s="14"/>
     </row>
-    <row r="9" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B9" s="15"/>
       <c r="C9" s="16"/>
       <c r="D9" s="16"/>
@@ -9905,7 +9954,7 @@
       <c r="O9" s="66"/>
       <c r="P9" s="16"/>
     </row>
-    <row r="10" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B10" s="17" t="s">
         <v>17</v>
       </c>
@@ -9952,162 +10001,263 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B11" s="20">
         <v>1</v>
       </c>
       <c r="C11" s="21" t="str">
         <f>IF(ISBLANK(D11), "", _xlfn.CONCAT("T", TEXT(B11, "0000"), "/", VLOOKUP(D11, Internal!$B$35:C$39, 2, FALSE()), IF(OR(D11="QA", D11="Revision"), _xlfn.CONCAT("/", H11), "")))</f>
-        <v/>
-      </c>
-      <c r="D11" s="22"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-      <c r="G11" s="22"/>
+        <v>T0001/M</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="F11" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>74</v>
+      </c>
       <c r="H11" s="23"/>
-      <c r="I11" s="24"/>
-      <c r="J11" s="24"/>
+      <c r="I11" s="24">
+        <v>46158.375</v>
+      </c>
+      <c r="J11" s="24">
+        <v>46158.416666666664</v>
+      </c>
       <c r="K11" s="25" t="str">
         <f t="shared" ref="K11:K42" ca="1" si="0">IF(OR(I11="",J11=""),"",IF(AND(J11&lt;&gt;"",I11&gt;=NOW()),"Planned",IF(AND(J11&lt;&gt;"",J11&lt;NOW()),"Completed","Ongoing")))</f>
-        <v/>
-      </c>
-      <c r="L11" s="26"/>
-      <c r="M11" s="26"/>
-      <c r="N11" s="25" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L11" s="26">
+        <v>1</v>
+      </c>
+      <c r="M11" s="26">
+        <v>1</v>
+      </c>
+      <c r="N11" s="25">
         <f>IF(ISBLANK(L11), "", L11*VLOOKUP($F11,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="O11" s="25" t="str">
+        <v>40</v>
+      </c>
+      <c r="O11" s="25">
         <f>IF(ISBLANK(M11), "", M11*VLOOKUP($F11,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="P11" s="22"/>
-    </row>
-    <row r="12" spans="2:16" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="P11" s="22" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B12" s="20">
         <v>2</v>
       </c>
       <c r="C12" s="21" t="str">
         <f>IF(ISBLANK(D12), "", _xlfn.CONCAT("T", TEXT(B12, "0000"), "/", VLOOKUP(D12, Internal!$B$35:C$39, 2, FALSE()), IF(OR(D12="QA", D12="Revision"), _xlfn.CONCAT("/", H12), "")))</f>
-        <v/>
-      </c>
-      <c r="D12" s="22"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="23"/>
-      <c r="I12" s="24"/>
-      <c r="J12" s="24"/>
+        <v>T0002/M</v>
+      </c>
+      <c r="D12" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="H12" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="I12" s="24">
+        <v>46158.416666666664</v>
+      </c>
+      <c r="J12" s="24">
+        <v>46158.458333333336</v>
+      </c>
       <c r="K12" s="25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L12" s="26"/>
-      <c r="M12" s="26"/>
-      <c r="N12" s="25" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L12" s="26">
+        <v>1</v>
+      </c>
+      <c r="M12" s="26">
+        <v>1</v>
+      </c>
+      <c r="N12" s="25">
         <f>IF(ISBLANK(L12), "", L12*VLOOKUP($F12,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="O12" s="25" t="str">
+        <v>40</v>
+      </c>
+      <c r="O12" s="25">
         <f>IF(ISBLANK(M12), "", M12*VLOOKUP($F12,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="P12" s="22"/>
-    </row>
-    <row r="13" spans="2:16" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+      <c r="P12" s="22" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B13" s="20">
         <v>3</v>
       </c>
       <c r="C13" s="21" t="str">
         <f>IF(ISBLANK(D13), "", _xlfn.CONCAT("T", TEXT(B13, "0000"), "/", VLOOKUP(D13, Internal!$B$35:C$39, 2, FALSE()), IF(OR(D13="QA", D13="Revision"), _xlfn.CONCAT("/", H13), "")))</f>
-        <v/>
-      </c>
-      <c r="D13" s="22"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="23"/>
-      <c r="I13" s="24"/>
-      <c r="J13" s="24"/>
+        <v>T0003/D</v>
+      </c>
+      <c r="D13" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="F13" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="H13" s="23" t="s">
+        <v>163</v>
+      </c>
+      <c r="I13" s="24">
+        <v>46158.458333333336</v>
+      </c>
+      <c r="J13" s="24">
+        <v>46158.666666666664</v>
+      </c>
       <c r="K13" s="25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L13" s="26"/>
-      <c r="M13" s="26"/>
-      <c r="N13" s="25" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L13" s="26">
+        <v>4</v>
+      </c>
+      <c r="M13" s="26">
+        <v>5</v>
+      </c>
+      <c r="N13" s="25">
         <f>IF(ISBLANK(L13), "", L13*VLOOKUP($F13,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="O13" s="25" t="str">
+        <v>100</v>
+      </c>
+      <c r="O13" s="25">
         <f>IF(ISBLANK(M13), "", M13*VLOOKUP($F13,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="P13" s="22"/>
-    </row>
-    <row r="14" spans="2:16" x14ac:dyDescent="0.3">
+        <v>125</v>
+      </c>
+      <c r="P13" s="22" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B14" s="20">
         <v>4</v>
       </c>
       <c r="C14" s="21" t="str">
         <f>IF(ISBLANK(D14), "", _xlfn.CONCAT("T", TEXT(B14, "0000"), "/", VLOOKUP(D14, Internal!$B$35:C$39, 2, FALSE()), IF(OR(D14="QA", D14="Revision"), _xlfn.CONCAT("/", H14), "")))</f>
-        <v/>
-      </c>
-      <c r="D14" s="22"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="24"/>
-      <c r="J14" s="24"/>
+        <v>T0004/QA/T0003/D</v>
+      </c>
+      <c r="D14" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="F14" s="23" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="H14" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="I14" s="24">
+        <v>46158.708333333336</v>
+      </c>
+      <c r="J14" s="24">
+        <v>46158.791666666664</v>
+      </c>
       <c r="K14" s="25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L14" s="26"/>
-      <c r="M14" s="26"/>
-      <c r="N14" s="25" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L14" s="26">
+        <v>2</v>
+      </c>
+      <c r="M14" s="26">
+        <v>2</v>
+      </c>
+      <c r="N14" s="25">
         <f>IF(ISBLANK(L14), "", L14*VLOOKUP($F14,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="O14" s="25" t="str">
+        <v>50</v>
+      </c>
+      <c r="O14" s="25">
         <f>IF(ISBLANK(M14), "", M14*VLOOKUP($F14,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="P14" s="22"/>
-    </row>
-    <row r="15" spans="2:16" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+      <c r="P14" s="22" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>168</v>
+      </c>
       <c r="B15" s="20">
         <v>5</v>
       </c>
       <c r="C15" s="21" t="str">
         <f>IF(ISBLANK(D15), "", _xlfn.CONCAT("T", TEXT(B15, "0000"), "/", VLOOKUP(D15, Internal!$B$35:C$39, 2, FALSE()), IF(OR(D15="QA", D15="Revision"), _xlfn.CONCAT("/", H15), "")))</f>
-        <v/>
-      </c>
-      <c r="D15" s="22"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="24"/>
-      <c r="J15" s="24"/>
+        <v>T0005/R/T0003/D</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="F15" s="23" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="H15" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="I15" s="24">
+        <v>46160.354166666664</v>
+      </c>
+      <c r="J15" s="24">
+        <v>46160.395833333336</v>
+      </c>
       <c r="K15" s="25" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v/>
-      </c>
-      <c r="L15" s="26"/>
-      <c r="M15" s="26"/>
-      <c r="N15" s="25" t="str">
+        <v>Completed</v>
+      </c>
+      <c r="L15" s="26">
+        <v>1</v>
+      </c>
+      <c r="M15" s="26">
+        <v>1</v>
+      </c>
+      <c r="N15" s="25">
         <f>IF(ISBLANK(L15), "", L15*VLOOKUP($F15,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="O15" s="25" t="str">
+        <v>0</v>
+      </c>
+      <c r="O15" s="25">
         <f>IF(ISBLANK(M15), "", M15*VLOOKUP($F15,Internal!$B$26:$C$32,2,FALSE()))</f>
-        <v/>
-      </c>
-      <c r="P15" s="22"/>
-    </row>
-    <row r="16" spans="2:16" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="P15" s="22" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B16" s="20">
         <v>6</v>
       </c>
@@ -10138,7 +10288,7 @@
       </c>
       <c r="P16" s="22"/>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B17" s="20">
         <v>7</v>
       </c>
@@ -10169,7 +10319,7 @@
       </c>
       <c r="P17" s="22"/>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B18" s="20">
         <v>8</v>
       </c>
@@ -10200,7 +10350,7 @@
       </c>
       <c r="P18" s="22"/>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B19" s="20">
         <v>9</v>
       </c>
@@ -10231,7 +10381,7 @@
       </c>
       <c r="P19" s="22"/>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B20" s="20">
         <v>10</v>
       </c>
@@ -10262,7 +10412,7 @@
       </c>
       <c r="P20" s="22"/>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B21" s="20">
         <v>11</v>
       </c>
@@ -10293,7 +10443,7 @@
       </c>
       <c r="P21" s="22"/>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B22" s="20">
         <v>12</v>
       </c>
@@ -10324,7 +10474,7 @@
       </c>
       <c r="P22" s="22"/>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B23" s="20">
         <v>13</v>
       </c>
@@ -10355,7 +10505,7 @@
       </c>
       <c r="P23" s="22"/>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B24" s="20">
         <v>14</v>
       </c>
@@ -10386,7 +10536,7 @@
       </c>
       <c r="P24" s="22"/>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B25" s="20">
         <v>15</v>
       </c>
@@ -10417,7 +10567,7 @@
       </c>
       <c r="P25" s="22"/>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B26" s="20">
         <v>16</v>
       </c>
@@ -10448,7 +10598,7 @@
       </c>
       <c r="P26" s="22"/>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B27" s="20">
         <v>17</v>
       </c>
@@ -10479,7 +10629,7 @@
       </c>
       <c r="P27" s="22"/>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B28" s="20">
         <v>18</v>
       </c>
@@ -10510,7 +10660,7 @@
       </c>
       <c r="P28" s="22"/>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B29" s="20">
         <v>19</v>
       </c>
@@ -10541,7 +10691,7 @@
       </c>
       <c r="P29" s="22"/>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B30" s="20">
         <v>20</v>
       </c>
@@ -10572,7 +10722,7 @@
       </c>
       <c r="P30" s="22"/>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B31" s="20">
         <v>21</v>
       </c>
@@ -10603,7 +10753,7 @@
       </c>
       <c r="P31" s="22"/>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B32" s="20">
         <v>22</v>
       </c>
@@ -10634,7 +10784,7 @@
       </c>
       <c r="P32" s="22"/>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B33" s="20">
         <v>23</v>
       </c>
@@ -10665,7 +10815,7 @@
       </c>
       <c r="P33" s="22"/>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B34" s="20">
         <v>24</v>
       </c>
@@ -10696,7 +10846,7 @@
       </c>
       <c r="P34" s="22"/>
     </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B35" s="20">
         <v>25</v>
       </c>
@@ -10727,7 +10877,7 @@
       </c>
       <c r="P35" s="22"/>
     </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B36" s="20">
         <v>26</v>
       </c>
@@ -10758,7 +10908,7 @@
       </c>
       <c r="P36" s="22"/>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B37" s="20">
         <v>27</v>
       </c>
@@ -10789,7 +10939,7 @@
       </c>
       <c r="P37" s="22"/>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B38" s="20">
         <v>28</v>
       </c>
@@ -10820,7 +10970,7 @@
       </c>
       <c r="P38" s="22"/>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B39" s="20">
         <v>29</v>
       </c>
@@ -10851,7 +11001,7 @@
       </c>
       <c r="P39" s="22"/>
     </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B40" s="20">
         <v>30</v>
       </c>
@@ -10882,7 +11032,7 @@
       </c>
       <c r="P40" s="22"/>
     </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B41" s="20">
         <v>31</v>
       </c>
@@ -10913,7 +11063,7 @@
       </c>
       <c r="P41" s="22"/>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B42" s="20">
         <v>32</v>
       </c>
@@ -10944,7 +11094,7 @@
       </c>
       <c r="P42" s="22"/>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B43" s="20">
         <v>33</v>
       </c>
@@ -10975,7 +11125,7 @@
       </c>
       <c r="P43" s="22"/>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B44" s="20">
         <v>34</v>
       </c>
@@ -11006,7 +11156,7 @@
       </c>
       <c r="P44" s="22"/>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B45" s="20">
         <v>35</v>
       </c>
@@ -11037,7 +11187,7 @@
       </c>
       <c r="P45" s="22"/>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B46" s="20">
         <v>36</v>
       </c>
@@ -11068,7 +11218,7 @@
       </c>
       <c r="P46" s="22"/>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B47" s="20">
         <v>37</v>
       </c>
@@ -11099,7 +11249,7 @@
       </c>
       <c r="P47" s="22"/>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B48" s="20">
         <v>38</v>
       </c>
@@ -11130,7 +11280,7 @@
       </c>
       <c r="P48" s="22"/>
     </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B49" s="20">
         <v>39</v>
       </c>
@@ -11161,7 +11311,7 @@
       </c>
       <c r="P49" s="22"/>
     </row>
-    <row r="50" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B50" s="20">
         <v>40</v>
       </c>
@@ -11192,7 +11342,7 @@
       </c>
       <c r="P50" s="22"/>
     </row>
-    <row r="51" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B51" s="20">
         <v>41</v>
       </c>
@@ -11223,7 +11373,7 @@
       </c>
       <c r="P51" s="22"/>
     </row>
-    <row r="52" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B52" s="20">
         <v>42</v>
       </c>
@@ -11254,7 +11404,7 @@
       </c>
       <c r="P52" s="22"/>
     </row>
-    <row r="53" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B53" s="20">
         <v>43</v>
       </c>
@@ -11285,7 +11435,7 @@
       </c>
       <c r="P53" s="22"/>
     </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B54" s="20">
         <v>44</v>
       </c>
@@ -11316,7 +11466,7 @@
       </c>
       <c r="P54" s="22"/>
     </row>
-    <row r="55" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="55" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B55" s="20">
         <v>45</v>
       </c>
@@ -11347,7 +11497,7 @@
       </c>
       <c r="P55" s="22"/>
     </row>
-    <row r="56" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="56" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B56" s="20">
         <v>46</v>
       </c>
@@ -11378,7 +11528,7 @@
       </c>
       <c r="P56" s="22"/>
     </row>
-    <row r="57" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="57" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B57" s="20">
         <v>47</v>
       </c>
@@ -11409,7 +11559,7 @@
       </c>
       <c r="P57" s="22"/>
     </row>
-    <row r="58" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="58" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B58" s="20">
         <v>48</v>
       </c>
@@ -11440,7 +11590,7 @@
       </c>
       <c r="P58" s="22"/>
     </row>
-    <row r="59" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="59" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B59" s="20">
         <v>49</v>
       </c>
@@ -11471,7 +11621,7 @@
       </c>
       <c r="P59" s="22"/>
     </row>
-    <row r="60" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="60" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B60" s="20">
         <v>50</v>
       </c>
@@ -11502,7 +11652,7 @@
       </c>
       <c r="P60" s="22"/>
     </row>
-    <row r="61" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="61" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B61" s="20">
         <v>51</v>
       </c>
@@ -11533,7 +11683,7 @@
       </c>
       <c r="P61" s="22"/>
     </row>
-    <row r="62" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B62" s="20">
         <v>52</v>
       </c>
@@ -11564,7 +11714,7 @@
       </c>
       <c r="P62" s="22"/>
     </row>
-    <row r="63" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="63" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B63" s="20">
         <v>53</v>
       </c>
@@ -11595,7 +11745,7 @@
       </c>
       <c r="P63" s="22"/>
     </row>
-    <row r="64" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B64" s="20">
         <v>54</v>
       </c>
@@ -11626,7 +11776,7 @@
       </c>
       <c r="P64" s="22"/>
     </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B65" s="20">
         <v>55</v>
       </c>
@@ -11657,7 +11807,7 @@
       </c>
       <c r="P65" s="22"/>
     </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="66" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B66" s="20">
         <v>56</v>
       </c>
@@ -11688,7 +11838,7 @@
       </c>
       <c r="P66" s="22"/>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B67" s="20">
         <v>57</v>
       </c>
@@ -11719,7 +11869,7 @@
       </c>
       <c r="P67" s="22"/>
     </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="68" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B68" s="20">
         <v>58</v>
       </c>
@@ -11750,7 +11900,7 @@
       </c>
       <c r="P68" s="22"/>
     </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B69" s="20">
         <v>59</v>
       </c>
@@ -11781,7 +11931,7 @@
       </c>
       <c r="P69" s="22"/>
     </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B70" s="20">
         <v>60</v>
       </c>
@@ -11812,7 +11962,7 @@
       </c>
       <c r="P70" s="22"/>
     </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B71" s="20">
         <v>61</v>
       </c>
@@ -11843,7 +11993,7 @@
       </c>
       <c r="P71" s="22"/>
     </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="72" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B72" s="20">
         <v>62</v>
       </c>
@@ -11874,7 +12024,7 @@
       </c>
       <c r="P72" s="22"/>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B73" s="20">
         <v>63</v>
       </c>
@@ -11905,7 +12055,7 @@
       </c>
       <c r="P73" s="22"/>
     </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="74" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B74" s="20">
         <v>64</v>
       </c>
@@ -11936,7 +12086,7 @@
       </c>
       <c r="P74" s="22"/>
     </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B75" s="20">
         <v>65</v>
       </c>
@@ -11967,7 +12117,7 @@
       </c>
       <c r="P75" s="22"/>
     </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B76" s="20">
         <v>66</v>
       </c>
@@ -11998,7 +12148,7 @@
       </c>
       <c r="P76" s="22"/>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B77" s="20">
         <v>67</v>
       </c>
@@ -12029,7 +12179,7 @@
       </c>
       <c r="P77" s="22"/>
     </row>
-    <row r="78" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="78" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B78" s="20">
         <v>68</v>
       </c>
@@ -12060,7 +12210,7 @@
       </c>
       <c r="P78" s="22"/>
     </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="79" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B79" s="20">
         <v>69</v>
       </c>
@@ -12091,7 +12241,7 @@
       </c>
       <c r="P79" s="22"/>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B80" s="20">
         <v>70</v>
       </c>
@@ -12122,7 +12272,7 @@
       </c>
       <c r="P80" s="22"/>
     </row>
-    <row r="81" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B81" s="20">
         <v>71</v>
       </c>
@@ -12153,7 +12303,7 @@
       </c>
       <c r="P81" s="22"/>
     </row>
-    <row r="82" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B82" s="20">
         <v>72</v>
       </c>
@@ -12184,7 +12334,7 @@
       </c>
       <c r="P82" s="22"/>
     </row>
-    <row r="83" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B83" s="20">
         <v>73</v>
       </c>
@@ -12215,7 +12365,7 @@
       </c>
       <c r="P83" s="22"/>
     </row>
-    <row r="84" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B84" s="20">
         <v>74</v>
       </c>
@@ -12246,7 +12396,7 @@
       </c>
       <c r="P84" s="22"/>
     </row>
-    <row r="85" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B85" s="20">
         <v>75</v>
       </c>
@@ -12277,7 +12427,7 @@
       </c>
       <c r="P85" s="22"/>
     </row>
-    <row r="86" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B86" s="20">
         <v>76</v>
       </c>
@@ -12308,7 +12458,7 @@
       </c>
       <c r="P86" s="22"/>
     </row>
-    <row r="87" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B87" s="20">
         <v>77</v>
       </c>
@@ -12339,7 +12489,7 @@
       </c>
       <c r="P87" s="22"/>
     </row>
-    <row r="88" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B88" s="20">
         <v>78</v>
       </c>
@@ -12370,7 +12520,7 @@
       </c>
       <c r="P88" s="22"/>
     </row>
-    <row r="89" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B89" s="20">
         <v>79</v>
       </c>
@@ -12401,7 +12551,7 @@
       </c>
       <c r="P89" s="22"/>
     </row>
-    <row r="90" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B90" s="20">
         <v>80</v>
       </c>
@@ -12432,7 +12582,7 @@
       </c>
       <c r="P90" s="22"/>
     </row>
-    <row r="91" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B91" s="20">
         <v>81</v>
       </c>
@@ -12463,7 +12613,7 @@
       </c>
       <c r="P91" s="22"/>
     </row>
-    <row r="92" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B92" s="20">
         <v>82</v>
       </c>
@@ -12494,7 +12644,7 @@
       </c>
       <c r="P92" s="22"/>
     </row>
-    <row r="93" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B93" s="20">
         <v>83</v>
       </c>
@@ -12525,7 +12675,7 @@
       </c>
       <c r="P93" s="22"/>
     </row>
-    <row r="94" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B94" s="20">
         <v>84</v>
       </c>
@@ -12556,7 +12706,7 @@
       </c>
       <c r="P94" s="22"/>
     </row>
-    <row r="95" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B95" s="20">
         <v>85</v>
       </c>
@@ -12587,7 +12737,7 @@
       </c>
       <c r="P95" s="22"/>
     </row>
-    <row r="96" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B96" s="20">
         <v>86</v>
       </c>
@@ -12618,7 +12768,7 @@
       </c>
       <c r="P96" s="22"/>
     </row>
-    <row r="97" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B97" s="20">
         <v>87</v>
       </c>
@@ -12649,7 +12799,7 @@
       </c>
       <c r="P97" s="22"/>
     </row>
-    <row r="98" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B98" s="20">
         <v>88</v>
       </c>
@@ -12680,7 +12830,7 @@
       </c>
       <c r="P98" s="22"/>
     </row>
-    <row r="99" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B99" s="20">
         <v>89</v>
       </c>
@@ -12711,7 +12861,7 @@
       </c>
       <c r="P99" s="22"/>
     </row>
-    <row r="100" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B100" s="20">
         <v>90</v>
       </c>
@@ -12742,7 +12892,7 @@
       </c>
       <c r="P100" s="22"/>
     </row>
-    <row r="101" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B101" s="20">
         <v>91</v>
       </c>
@@ -12773,7 +12923,7 @@
       </c>
       <c r="P101" s="22"/>
     </row>
-    <row r="102" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B102" s="20">
         <v>92</v>
       </c>
@@ -12804,7 +12954,7 @@
       </c>
       <c r="P102" s="22"/>
     </row>
-    <row r="103" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B103" s="20">
         <v>93</v>
       </c>
@@ -12835,7 +12985,7 @@
       </c>
       <c r="P103" s="22"/>
     </row>
-    <row r="104" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B104" s="20">
         <v>94</v>
       </c>
@@ -12866,7 +13016,7 @@
       </c>
       <c r="P104" s="22"/>
     </row>
-    <row r="105" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B105" s="20">
         <v>95</v>
       </c>
@@ -12897,7 +13047,7 @@
       </c>
       <c r="P105" s="22"/>
     </row>
-    <row r="106" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B106" s="20">
         <v>96</v>
       </c>
@@ -12928,7 +13078,7 @@
       </c>
       <c r="P106" s="22"/>
     </row>
-    <row r="107" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B107" s="20">
         <v>97</v>
       </c>
@@ -12959,7 +13109,7 @@
       </c>
       <c r="P107" s="22"/>
     </row>
-    <row r="108" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B108" s="20">
         <v>98</v>
       </c>
@@ -12990,7 +13140,7 @@
       </c>
       <c r="P108" s="22"/>
     </row>
-    <row r="109" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B109" s="20">
         <v>99</v>
       </c>
@@ -13021,7 +13171,7 @@
       </c>
       <c r="P109" s="22"/>
     </row>
-    <row r="110" spans="2:16" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B110" s="20">
         <v>100</v>
       </c>
@@ -13168,12 +13318,12 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B2:J39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B2" s="63" t="s">
         <v>88</v>
       </c>
@@ -13186,7 +13336,7 @@
       <c r="I2" s="63"/>
       <c r="J2" s="63"/>
     </row>
-    <row r="4" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10" ht="14" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B4" s="64" t="s">
         <v>89</v>
       </c>
@@ -13199,7 +13349,7 @@
       <c r="I4" s="64"/>
       <c r="J4" s="64"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B5" s="64"/>
       <c r="C5" s="64"/>
       <c r="D5" s="64"/>
@@ -13210,7 +13360,7 @@
       <c r="I5" s="64"/>
       <c r="J5" s="64"/>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B6" s="64"/>
       <c r="C6" s="64"/>
       <c r="D6" s="64"/>
@@ -13221,7 +13371,7 @@
       <c r="I6" s="64"/>
       <c r="J6" s="64"/>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
       <c r="D7" s="9"/>
@@ -13232,7 +13382,7 @@
       <c r="I7" s="9"/>
       <c r="J7" s="9"/>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B8" s="29" t="s">
         <v>90</v>
       </c>
@@ -13245,7 +13395,7 @@
       <c r="I8" s="30"/>
       <c r="J8" s="30"/>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B9" s="31" t="s">
         <v>91</v>
       </c>
@@ -13258,7 +13408,7 @@
       <c r="I9" s="30"/>
       <c r="J9" s="30"/>
     </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B10" s="31" t="s">
         <v>92</v>
       </c>
@@ -13271,7 +13421,7 @@
       <c r="I10" s="30"/>
       <c r="J10" s="30"/>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B11" s="31" t="s">
         <v>31</v>
       </c>
@@ -13284,7 +13434,7 @@
       <c r="I11" s="30"/>
       <c r="J11" s="30"/>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B12" s="31" t="s">
         <v>36</v>
       </c>
@@ -13297,7 +13447,7 @@
       <c r="I12" s="30"/>
       <c r="J12" s="30"/>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B13" s="31" t="s">
         <v>93</v>
       </c>
@@ -13310,7 +13460,7 @@
       <c r="I13" s="30"/>
       <c r="J13" s="30"/>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B14" s="32" t="s">
         <v>94</v>
       </c>
@@ -13323,7 +13473,7 @@
       <c r="I14" s="30"/>
       <c r="J14" s="30"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B15" s="8"/>
       <c r="C15" s="30"/>
       <c r="D15" s="30"/>
@@ -13334,7 +13484,7 @@
       <c r="I15" s="30"/>
       <c r="J15" s="30"/>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B16" s="33" t="s">
         <v>95</v>
       </c>
@@ -13347,7 +13497,7 @@
       <c r="I16" s="30"/>
       <c r="J16" s="30"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B17" s="34" t="s">
         <v>96</v>
       </c>
@@ -13360,7 +13510,7 @@
       <c r="I17" s="30"/>
       <c r="J17" s="30"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B18" s="34" t="s">
         <v>97</v>
       </c>
@@ -13373,7 +13523,7 @@
       <c r="I18" s="30"/>
       <c r="J18" s="30"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B19" s="35" t="s">
         <v>98</v>
       </c>
@@ -13386,7 +13536,7 @@
       <c r="I19" s="30"/>
       <c r="J19" s="30"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B20" s="8"/>
       <c r="C20" s="30"/>
       <c r="D20" s="30"/>
@@ -13397,7 +13547,7 @@
       <c r="I20" s="30"/>
       <c r="J20" s="30"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B21" s="33" t="s">
         <v>99</v>
       </c>
@@ -13410,7 +13560,7 @@
       <c r="I21" s="30"/>
       <c r="J21" s="30"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B22" s="36">
         <v>45658</v>
       </c>
@@ -13423,7 +13573,7 @@
       <c r="I22" s="30"/>
       <c r="J22" s="30"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B23" s="37">
         <v>46062.354166666701</v>
       </c>
@@ -13436,7 +13586,7 @@
       <c r="I23" s="30"/>
       <c r="J23" s="30"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B24" s="30"/>
       <c r="C24" s="30"/>
       <c r="D24" s="30"/>
@@ -13447,7 +13597,7 @@
       <c r="I24" s="30"/>
       <c r="J24" s="30"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B25" s="38" t="s">
         <v>100</v>
       </c>
@@ -13464,7 +13614,7 @@
       <c r="I25" s="40"/>
       <c r="J25" s="41"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B26" s="42" t="s">
         <v>76</v>
       </c>
@@ -13487,7 +13637,7 @@
       <c r="I26" s="30"/>
       <c r="J26" s="44"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B27" s="42" t="s">
         <v>45</v>
       </c>
@@ -13514,7 +13664,7 @@
       </c>
       <c r="J27" s="44"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B28" s="42" t="s">
         <v>73</v>
       </c>
@@ -13539,7 +13689,7 @@
       <c r="I28" s="30"/>
       <c r="J28" s="44"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B29" s="42" t="s">
         <v>37</v>
       </c>
@@ -13566,7 +13716,7 @@
       </c>
       <c r="J29" s="44"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B30" s="42" t="s">
         <v>56</v>
       </c>
@@ -13593,7 +13743,7 @@
       </c>
       <c r="J30" s="44"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B31" s="45" t="s">
         <v>32</v>
       </c>
@@ -13622,7 +13772,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B32" s="46" t="s">
         <v>115</v>
       </c>
@@ -13639,7 +13789,7 @@
       <c r="I32" s="48"/>
       <c r="J32" s="49"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B33" s="30"/>
       <c r="C33" s="30"/>
       <c r="D33" s="30"/>
@@ -13650,7 +13800,7 @@
       <c r="I33" s="30"/>
       <c r="J33" s="30"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B34" s="50" t="s">
         <v>116</v>
       </c>
@@ -13665,7 +13815,7 @@
       <c r="I34" s="30"/>
       <c r="J34" s="30"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B35" s="45" t="s">
         <v>30</v>
       </c>
@@ -13680,7 +13830,7 @@
       <c r="I35" s="30"/>
       <c r="J35" s="30"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B36" s="45" t="s">
         <v>35</v>
       </c>
@@ -13695,7 +13845,7 @@
       <c r="I36" s="30"/>
       <c r="J36" s="30"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B37" s="45" t="s">
         <v>55</v>
       </c>
@@ -13710,7 +13860,7 @@
       <c r="I37" s="30"/>
       <c r="J37" s="30"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B38" s="45" t="s">
         <v>72</v>
       </c>
@@ -13725,7 +13875,7 @@
       <c r="I38" s="30"/>
       <c r="J38" s="30"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.35">
       <c r="B39" s="52" t="s">
         <v>115</v>
       </c>
